--- a/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
+++ b/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
@@ -457,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -526,7 +526,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Partner / co-lead (sports-media exec: Skadden, FanDuel, DAZN, FTX; minority owner Ipswich Town, Frosinone)</t>
+          <t>Partner/co-lead (Skadden, FanDuel, DAZN, FTX; minority owner Ipswich Town, Frosinone)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Core partner; on nearly every thread</t>
+          <t>On nearly every thread since inception</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Active — daily</t>
+          <t>Active — core</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Leading the parent-co / franchise-fee raise track; investor one-pager</t>
+          <t>Leads parent-co/franchise-fee raise; investor one-pager</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Most active outside partner; drove branding + investor one-pager</t>
+          <t>Most active outside partner</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -583,206 +583,206 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Active — Aug 14 call w/ Paul &amp; Mark</t>
+          <t>Active — Aug 14 call</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Anurag (confirm last name)</t>
+          <t>Greg Kristof</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>(w/ Ankur / Tabor)</t>
+          <t>6th Sense Consulting</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Investor-side; joined Ankur/Norm/Sunjay calls</t>
+          <t>Partner — OWNS ~4% of parent co; schools + NCAA-units</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>anurag41@gmail.com</t>
+          <t>greg@6sc.io</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>On Ankur's investor calls</t>
+          <t>Principal-level; Merrimack intro</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Active — confirm role</t>
+          <t>Active — ~4% stakeholder; Merrimack call</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Paul Magahis</t>
+          <t>Breanna Powers Kirk</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
+          <t>6th Sense Consulting</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Investor / partner on 'Paul &amp; Mark' calls</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>pmagahis@gmail.com</t>
+          <t>breanna@6sc.io</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Recurring calls w/ Ankur</t>
+          <t>6SC intro call</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Active — Aug 14 call</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Greg Kristof</t>
+          <t>Anurag (confirm surname)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>6th Sense Consulting</t>
+          <t>(w/ Ankur / Tabor)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Partner; schools + NCAA-units research, Merrimack intro</t>
+          <t>Investor-side; on Ankur calls</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>greg@6sc.io</t>
+          <t>anurag41@gmail.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Deeply involved; 'is he 100% in?' per Ankur</t>
+          <t>Ankur's investor calls</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Active — Merrimack call Aug 19; confirm formal role</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Breanna Powers Kirk</t>
+          <t>Paul Magahis</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>6th Sense Consulting</t>
+          <t>NYC private (confirm)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Potential parent-co investor — wealthy (uncle wealthier)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>breanna@6sc.io</t>
+          <t>pmagahis@gmail.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Joined 6SC intro call</t>
+          <t>Meeting Fri Aug 14 w/ 'Mark'</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>HOT — Aug 14 investor mtg (Paul &amp; Mark)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Capital / Investors</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Cullen Gilchrist</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>(food entrepreneur, D.C.)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Close friend/ally — wants to buy a sports team</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>cullen.gilchrist@gmail.com</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Personal ally; early sounding board</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Ally — keep looped</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Vasu Kulkarni</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Courtside VC</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>vasu@courtsidevc.com</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Courtside team met re: project</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Met — follow up</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Capital / Investors  (all active per Norman)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Kai Bond</t>
+          <t>Vasu Kulkarni</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>kai@courtsidevc.com</t>
+          <t>vasu@courtsidevc.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Oliver Ressler</t>
+          <t>Kai Bond</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -827,10 +827,14 @@
           <t>Courtside VC</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>oliver@courtsidevc.com</t>
+          <t>kai@courtsidevc.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -845,14 +849,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Will Johnson</t>
+          <t>Oliver Ressler</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -863,7 +867,7 @@
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>will@courtsidevc.com</t>
+          <t>oliver@courtsidevc.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -878,14 +882,14 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Cort Post</t>
+          <t>Will Johnson</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -896,7 +900,7 @@
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>cort@courtsidevc.com</t>
+          <t>will@courtsidevc.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -911,14 +915,14 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Deepen (confirm last name)</t>
+          <t>Cort Post</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -926,19 +930,15 @@
           <t>Courtside VC</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Organized Courtside meeting</t>
-        </is>
-      </c>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>deepen@courtsidevc.com</t>
+          <t>cort@courtsidevc.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Set the Courtside call</t>
+          <t>Courtside team</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -948,34 +948,34 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Matt Kim</t>
+          <t>Deepen (confirm surname)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Mubadala Capital</t>
+          <t>Courtside VC</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>Set the Courtside call</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>mkim@mubadalacapital.ae</t>
+          <t>deepen@courtsidevc.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Mubadala call</t>
+          <t>Courtside organizer</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -985,56 +985,56 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Matt Sherman</t>
+          <t>Matt Kim</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>TFO Equity / TFO Sports</t>
+          <t>Mubadala Capital</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Investor; set TFO call</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>matt.sherman@tfoequity.com</t>
+          <t>mkim@mubadalacapital.ae</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>TFO Sports meeting</t>
+          <t>Long thread since June</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active — follow up</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>David Foster</t>
+          <t>A. Safavi (confirm)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>TFO Equity</t>
+          <t>Mubadala Capital</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1044,71 +1044,71 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>david.foster@tfoequity.com</t>
+          <t>asafavi@mubadalacapital.ae</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>TFO Sports meeting</t>
+          <t>Intro w/ Matt Kim</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>JJ (confirm)</t>
+          <t>Matt Sherman</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>The Chernin Group</t>
+          <t>TFO Equity / TFO Sports</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Development / investment (Peter Chernin, Jesse Jacobs org)</t>
+          <t>Investor; set TFO call</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>jj@cherninent.com</t>
+          <t>matt.sherman@tfoequity.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>TCG = lead funding+dev per vault</t>
+          <t>TFO Sports</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Active thread — confirm contact name</t>
+          <t>Active — follow up</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Kitan (confirm last name)</t>
+          <t>David Foster</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Dynasty Equity</t>
+          <t>TFO Equity</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1118,49 +1118,49 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>kitan@dynastyequity.com</t>
+          <t>david.foster@tfoequity.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Dynasty Equity contact</t>
+          <t>TFO Sports</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Adrian Williams</t>
+          <t>Jesse Jacobs</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>SC Holdings</t>
+          <t>The Chernin Group (TCG)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>Lead funding + development (w/ Peter Chernin)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>adrian@sc.holdings</t>
+          <t>jj@cherninent.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SC Holdings</t>
+          <t>TCG = lead funding+dev per vault</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1170,19 +1170,19 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active — key</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Chuck (confirm last name)</t>
+          <t>Kitan (confirm surname)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Winnie Capital</t>
+          <t>Dynasty Equity</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1192,34 +1192,34 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>chuck@winniecap.com</t>
+          <t>kitan@dynastyequity.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Winnie Capital</t>
+          <t>Long June/July thread</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active — follow up</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Chip (confirm last name)</t>
+          <t>J. Leary (confirm)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Eight State</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1229,71 +1229,71 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>chip@eightstate.com</t>
+          <t>jleary@sixthstreet.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Eight State</t>
+          <t>May/June thread</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active — follow up</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Nathaniel (confirm last name)</t>
+          <t>Ishu (confirm surname)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>DGB.vc</t>
+          <t>Main Street Advisors (Paul Wachter)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>Investor / advisor</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>nathaniel@dgb.vc</t>
+          <t>ishu@mainstreetadvisors.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>DGB VC</t>
+          <t>Recontacted Aug 12; Wachter = principal</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active — re-engaged</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Eric (confirm last name)</t>
+          <t>T. Marcy (confirm)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>VaynerWatt</t>
+          <t>Avenue Capital</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1303,34 +1303,34 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>eric@vaynerwatt.com</t>
+          <t>tmarcy@avenuecapital.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>VaynerWatt team</t>
+          <t>w/ J. Greenbaum</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Sam (confirm last name)</t>
+          <t>J. Greenbaum (confirm)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>VaynerWatt</t>
+          <t>Avenue Capital</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1340,243 +1340,251 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>sam@vaynerwatt.com</t>
+          <t>jgreenbaum@avenuecapital.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>VaynerWatt team</t>
+          <t>cc on Avenue thread</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Aaron (confirm last name)</t>
+          <t>W. Hess (confirm)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Paul Street</t>
+          <t>645 Ventures</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>On Just Train / Making Cinderella calls</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>aaron@paulstreet.co</t>
+          <t>whess@645ventures.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Joined Kalani/Just Train calls</t>
+          <t>June/July thread</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Confirm role (investor vs talent-side)</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Eric Paredes</t>
+          <t>Maya (confirm surname)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>JP Morgan</t>
+          <t>Left Lane Capital</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>eric.a.paredes@jpmorgan.com</t>
+          <t>maya@leftlane.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Cinderella Corp thread</t>
+          <t>w/ Laura</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Confirm status</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Allen Cheng</t>
+          <t>Laura (confirm surname)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
+          <t>Left Lane Capital</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Investor / advisor</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>allen@allencheng.com</t>
+          <t>laura@leftlane.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>On calendar</t>
+          <t>Left Lane team</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Confirm status</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Hunter Reinhart</t>
+          <t>B. Sharma (confirm)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
+          <t>Bluestone Equity</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Organized a meeting</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>hunterreinhart@gmail.com</t>
+          <t>bsharma@bluestoneequity.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Meeting organizer on calendar</t>
+          <t>May thread (via Sunjay)</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Jeremy Peschka</t>
+          <t>A. Howard (confirm)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
+          <t>Shamrock Capital</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>jeremy.peschka@gmail.com</t>
+          <t>AHoward@shamrockcap.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>On calendar</t>
+          <t>bcc'd on ROS thread</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Varun Sudhakar</t>
+          <t>P. Blacklow (confirm)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr"/>
+          <t>Boston Seed</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>varun.sudhakar13@gmail.com</t>
+          <t>pblacklow@bostonseed.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>On calendar</t>
+          <t>One-off outreach</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>(confirm) barwinca</t>
+          <t>Marc Gottesman</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1584,170 +1592,204 @@
           <t>(confirm org)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Investor — likely your 'mags'</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>barwinca@gmail.com</t>
+          <t>marc.gottesman1@gmail.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>On calendar</t>
+          <t>One-off outreach May</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Confirm — 'mags'? revisit</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Celebrity Reps / Agents / Talent Camps</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Chuck (confirm surname)</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Winnie Capital</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>chuck@winniecap.com</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Darren Prince</t>
+          <t>Chip (confirm surname)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Prince Marketing Group</t>
+          <t>Eight State</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Founder/CEO — agent (Magic Johnson, Bird, Pippen, Goggins, etc.)</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>dprince@princemarketinggroup.com</t>
+          <t>chip@eightstate.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Warm text-&gt;email; handed to Mathilda</t>
+          <t>w/ Elisa</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Active — via Mathilda</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Mathilda Tennysdotter</t>
+          <t>Elisa (confirm surname)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Prince Marketing Group</t>
+          <t>Eight State</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>COO, Talent Representation</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>mathilda@princemarketinggroup.com</t>
+          <t>elisa@eightstate.com</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Suggesting names; you replied w/ ask+comp</t>
+          <t>Eight State team</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE — awaiting her names; call offered</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Kevin Gelbard</t>
+          <t>Nathaniel (confirm surname)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>DGB.vc</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Agent — reps Ludacris, Tim McGraw</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>kevin.gelbard@caa.com</t>
+          <t>nathaniel@dgb.vc</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Agreed to pass to Luda &amp; Tim's teams</t>
+          <t>One-off June</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Active — awaiting pass-through</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>David Sherman</t>
+          <t>Adrian Williams</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>WME</t>
+          <t>SC Holdings</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Non-scripted side</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>dsherman@wmeagency.com</t>
+          <t>adrian@sc.holdings</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Existing connection per vault</t>
+          <t>On calendar</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -1757,104 +1799,108 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Warm — reconnect</t>
+          <t>Confirm status</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>DJS (confirm name)</t>
+          <t>Eric (confirm surname)</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>WME</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr"/>
+          <t>VaynerWatt</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>djs@wmeagency.com</t>
+          <t>eric@vaynerwatt.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>On WME calendar invite</t>
+          <t>w/ Sam</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Erick Peyton</t>
+          <t>Sam (confirm surname)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Unanimous Media (Steph Curry)</t>
+          <t>VaynerWatt</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Exec — Curry/Davidson pairing</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>erick@unanimousmedia.com</t>
+          <t>sam@vaynerwatt.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Curry/Davidson attached via Unanimous</t>
+          <t>VaynerWatt team</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Active — flagship pairing</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Ron 'Boss' Everline</t>
+          <t>Aaron (confirm surname)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Just Train (Kevin Hart's trainer/biz partner)</t>
+          <t>Paul Street</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Principal — Hart camp</t>
+          <t>On Hart/Just Train + investor calls</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>boss@just-train.com</t>
+          <t>aaron@paulstreet.co</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Hart -&gt; St. Joe's path</t>
+          <t>Recurring since May</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -1864,506 +1910,522 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Active — Hart channel</t>
+          <t>Active — confirm role</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Kalani Jones</t>
+          <t>Eric Paredes</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Just Train</t>
+          <t>JP Morgan</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Scheduling / ops (Hart camp)</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>kalani@just-train.com</t>
+          <t>eric.a.paredes@jpmorgan.com</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Set the Just Train Zoom calls</t>
+          <t>Cinderella Corp thread</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Active — Hart channel</t>
+          <t>Confirm status</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Jay Jackson</t>
+          <t>Jordan (confirm surname)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Humain Pro</t>
+          <t>Cymbul</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Talent-side; 'Shane/Jay' outline</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>jay@humainpro.com</t>
+          <t>jordan@cymbul.co</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Negotiating alignment/role</t>
+          <t>One-off May</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Active — terms discussion</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Shane Duffy</t>
+          <t>Nate Fritsch</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Humain Pro (confirm)</t>
+          <t>Kaba AI</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Talent-side; with Jay</t>
+          <t>Investor / advisor</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>seoda70@gmail.com</t>
+          <t>nate.fritsch@kaba.ai</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>'Shane/Jay' pairing</t>
+          <t>One-off April</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Active — terms discussion</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Jason Bernstein</t>
+          <t>Allen Cheng</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Clarity Football</t>
+          <t>(confirm org)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Agent — Jason Kelce</t>
+          <t>Investor / advisor</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>jason@clarityfootball.com</t>
+          <t>allen@allencheng.com</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Kelce deck sent (St. Joe's)</t>
+          <t>On calendar</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Active — Kelce channel</t>
+          <t>Confirm status</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Corey Smyth</t>
+          <t>Hunter Reinhart</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Blacksmith (NYC)</t>
+          <t>(confirm org)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Gatekeeper / manager (Netflix + celeb access)</t>
+          <t>Meeting organizer</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>csmyth@blacksmithnyc.com</t>
+          <t>hunterreinhart@gmail.com</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>'Gatekeeper' per your GW note</t>
+          <t>Set a meeting June</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Active — sent deck</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Kristen (confirm last name)</t>
+          <t>Jeremy Peschka</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Vanguard Sports</t>
+          <t>(confirm org; House of Gambel?)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Investor / connect</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>kristen@vanguardsports.com</t>
+          <t>jeremy.peschka@gmail.com</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>On calendar</t>
+          <t>w/ houseofgambel@gmail.com</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Confirm status</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Production / Streamers</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Varun Sudhakar</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>(confirm org)</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Investor / connect</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>varun.sudhakar13@gmail.com</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>June threads</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Rebecca 'Becca' Gitlitz</t>
+          <t>(confirm) barwinca</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>EverWonder</t>
+          <t>(confirm) SJU-connected</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Production lead — deck edits</t>
+          <t>Intermediary w/ Saint Joseph's</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>rebecca.gitlitz@gmail.com</t>
+          <t>barwinca@gmail.com</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Iterating the production deck w/ you</t>
+          <t>Cc'd on SJU/Mihalich threads</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Active — deck collaboration</t>
+          <t>Confirm identity (SJU booster?)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Deirdre Fenton</t>
+          <t>(confirm) ddilieg</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>EverWonder</t>
+          <t>(confirm org)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Intro / exec</t>
+          <t>Connect</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>deirdre.a.fenton@gmail.com</t>
+          <t>ddilieg@gmail.com</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Introduced EverWonder</t>
+          <t>Starred back-and-forth July</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Clara Lawry</t>
+          <t>David Famolari</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EverWonder</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr"/>
+          <t>(confirm org — Verizon Ventures?)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Investor — YOU flagged, not found in email</t>
+        </is>
+      </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>clara.lawry@everwonder.studio</t>
+          <t>(confirm email)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>EverWonder team on calendar</t>
+          <t>You named as a VC to include</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Add — confirm contact info</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Ian (confirm last name)</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>EverWonder</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr"/>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>ian@everwonder.studio</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>EverWonder team</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Team member</t>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Celebrity Reps / Agents / Talent Camps</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Mike (confirm last name)</t>
+          <t>Darren Prince</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EverWonder</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr"/>
+          <t>Prince Marketing Group</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Founder/CEO — agent (Magic, Bird, Pippen, Goggins...)</t>
+        </is>
+      </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>mike@everwonder.studio</t>
+          <t>dprince@princemarketinggroup.com</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>EverWonder team</t>
+          <t>Warm intro; handed to Mathilda</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Jonathan Schaerf</t>
+          <t>Mathilda Tennysdotter</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
+          <t>Prince Marketing Group</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Exec</t>
+          <t>COO, Talent Rep</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>jonathan@religionofsports.com</t>
+          <t>mathilda@princemarketinggroup.com</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>ROS x Norman Zoom</t>
+          <t>Suggesting names; call offered</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>HOT — awaiting names</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Max Kramer</t>
+          <t>Kevin Gelbard</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Set the ROS Zoom</t>
+          <t>Agent — Ludacris, Tim McGraw</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>max.kramer@religionofsports.com</t>
+          <t>kevin.gelbard@caa.com</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Scheduled ROS call</t>
+          <t>Passing to Luda &amp; Tim teams</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active — awaiting pass-through</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Pietro Moro</t>
+          <t>David Sherman</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr"/>
+          <t>WME</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Non-scripted</t>
+        </is>
+      </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>pietro@religionofsports.com</t>
+          <t>dsherman@wmeagency.com</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>ROS team</t>
+          <t>Existing connection</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2373,30 +2435,30 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Warm — reconnect</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Todd Barrish</t>
+          <t>DJS (confirm name)</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
+          <t>WME</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr"/>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>todd.barrish@religionofsports.com</t>
+          <t>djs@wmeagency.com</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>ROS team</t>
+          <t>WME calendar invite</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2406,817 +2468,839 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Victoria Del Rossi</t>
+          <t>Erick Peyton</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Candle Studios (Candle Media)</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr"/>
+          <t>Unanimous Media (Steph Curry)</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Exec — Curry/Davidson</t>
+        </is>
+      </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>victoria.delrossi@candlestudios.com</t>
+          <t>erick@unanimousmedia.com</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Candle Studios call</t>
+          <t>Flagship pairing since May</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Met — follow up</t>
+          <t>Active — flagship</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>A. Schneider (confirm)</t>
+          <t>Ron 'Boss' Everline</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Candle Studios</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr"/>
+          <t>Just Train / Hartbeat Ventures (Kevin Hart)</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Principal — Hart camp</t>
+        </is>
+      </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>aschneider@candlestudios.com</t>
+          <t>boss@just-train.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Candle Studios</t>
+          <t>Hart -&gt; St. Joe's</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Active — Hart channel (also boss@hartbeatventures.com)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Josh (confirm last name)</t>
+          <t>Kalani Jones</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Straylight Productions</t>
+          <t>Just Train</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Ops/scheduling (Hart camp)</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>jtb@straylightprod.co</t>
+          <t>kalani@just-train.com</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Production decks + Becca edits</t>
+          <t>Set Just Train Zooms</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Active — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Schools (ADs / Coaches / Staff)</t>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Jay Jackson</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Humain Pro</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Talent-side; 'Shane/Jay' outline</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>jay@humainpro.com</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Terms/alignment discussion</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Ashwin Puri</t>
+          <t>Shane Duffy</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's (SJU)</t>
+          <t>Humain Pro (confirm)</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>CFO — signed the LOI</t>
+          <t>Talent-side; with Jay</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>apuri@sju.edu</t>
+          <t>seoda70@gmail.com</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>LOI signed 7/29</t>
+          <t>'Shane/Jay'</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>LOI SIGNED — advance to MMR/Van Wagner</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Joseph Mihalich</t>
+          <t>Alan (confirm surname)</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's (SJU)</t>
+          <t>(w/ Humain — n9.lol)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Athletics (confirm exact title)</t>
+          <t>Talent-side; on Shane/Jay thread</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>jmihalich@sju.edu</t>
+          <t>alan@n9.lol</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>On SJU MMR discussion</t>
+          <t>cc on Humain thread</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>(SJU staff) elaudano</t>
+          <t>Jason Bernstein</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's</t>
+          <t>Clarity Football</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>(confirm)</t>
+          <t>Agent — Jason Kelce</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>elaudano@sju.edu</t>
+          <t>jason@clarityfootball.com</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>SJU calendar</t>
+          <t>Kelce deck (St. Joe's)</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Active — Kelce</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>(SJU staff) freynolds</t>
+          <t>Corey Smyth</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's</t>
+          <t>Blacksmith (NYC)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>(confirm)</t>
+          <t>Manager/gatekeeper (Netflix + celeb access)</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>freynolds@sju.edu</t>
+          <t>csmyth@blacksmithnyc.com</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>SJU calendar</t>
+          <t>'Gatekeeper' per your note</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Active — sent deck</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>(SJU staff) kwelsh</t>
+          <t>Kristen (confirm surname)</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's</t>
+          <t>Vanguard Sports Group</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>(confirm)</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>kwelsh@sju.edu</t>
+          <t>kristen@vanguardsports.com</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>SJU calendar</t>
+          <t>April thread</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Cold — revisit (also @vanguardsportsgroup.com)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>(SJU staff) sdonahue1</t>
+          <t>E. Thomas (confirm)</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's</t>
+          <t>Happy Madison (Adam Sandler)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>(confirm)</t>
+          <t>Sandler's company</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>sdonahue1@sju.edu</t>
+          <t>ethomas@happymadison.net</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>SJU calendar</t>
+          <t>Sandler channel (some bounced)</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Cold — verify address</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>(SJU staff) tpachman</t>
+          <t>Stephen (confirm surname)</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>(confirm)</t>
+          <t>Rep — Steve Nash channel</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>tpachman@sju.edu</t>
+          <t>ctrlstephen@gmail.com</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>SJU calendar</t>
+          <t>Nash via CTRL direct</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Chris Caputo</t>
+          <t>Alan Nierob</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>George Washington (GW)</t>
+          <t>Rogers &amp; Cowan PMK</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Head Men's Basketball Coach</t>
+          <t>Hollywood publicist</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>coachcaputo@gwu.edu</t>
+          <t>alan.nierob@rogersandcowanpmk.com</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Championed to his AD</t>
+          <t>One-off outreach May</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Active — met 8/7</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Michael Lipitz</t>
+          <t>Brian Scalabrine</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>George Washington (GW)</t>
+          <t>(former NBA / broadcaster)</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Athletic Director</t>
+          <t>Talent / celebrity</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>michael.lipitz@email.gwu.edu</t>
+          <t>bscalabrine@yahoo.com</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Met 8/7</t>
+          <t>Direct outreach June</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Active — post-meeting follow up</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Chris Clunie</t>
+          <t>G. Cheddy (confirm)</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>BEP-LA</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Athletic Director (confirm)</t>
+          <t>Talent/brand</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>chclunie@davidson.edu</t>
+          <t>g.cheddy@bep-la.com</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Davidson (Curry flagship)</t>
+          <t>Earliest outreach (Feb/Apr)</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Active — flagship school</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Nathan Davis</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>New Hampshire (UNH)</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>Head Coach (confirm)</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>nathan.davis@unh.edu</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>LOI draft sent</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>Active — LOI in play</t>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Production / Streamers / Media</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>J. Gallo (confirm)</t>
+          <t>Rebecca 'Becca' Gitlitz</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Merrimack</t>
+          <t>EverWonder</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>Production lead — deck edits</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>galloj@merrimack.edu</t>
+          <t>rebecca.gitlitz@gmail.com</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Merrimack call Aug 19</t>
+          <t>Iterating production deck</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Active — call scheduled</t>
+          <t>Active — lead partner</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>'Coach New' (confirm identity)</t>
+          <t>Deirdre Fenton</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>(confirm school)</t>
+          <t>EverWonder</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Coach — received names list</t>
+          <t>Exec — introduced EverWonder</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>coachenew@gmail.com</t>
+          <t>deirdre.a.fenton@gmail.com</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Sent school/celeb names</t>
+          <t>Since May</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Active — confirm who this is</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Chris Herren</t>
+          <t>Clara Lawry</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>(former NBA / speaker)</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Talent / advocate</t>
-        </is>
-      </c>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr"/>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>chris@chrisherren.com</t>
+          <t>clara.lawry@everwonder.studio</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>'WtW meets college hoops' pitch</t>
+          <t>EverWonder team</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Legal</t>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Ian (confirm surname)</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>ian@everwonder.studio</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>EverWonder team</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Grant Darwin</t>
+          <t>Mike (confirm surname)</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr"/>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>gdarwin@proskauer.com</t>
+          <t>mike@everwonder.studio</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Proskauer team</t>
+          <t>EverWonder team</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Legal — confirm engagement</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Kyle Casazza</t>
+          <t>Ameeth Sankaran (confirm)</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
+          <t>Religion of Sports</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>Founder/exec</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>kcasazza@proskauer.com</t>
+          <t>ameeth@religionofsports.com</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Proskauer team</t>
+          <t>ROS lead thread (Apr)</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Robert Freeman</t>
+          <t>Jonathan Schaerf</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
+          <t>Religion of Sports</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Attorney (set meeting)</t>
+          <t>Exec</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>rfreeman@proskauer.com</t>
+          <t>jonathan@religionofsports.com</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Proskauer call organizer</t>
+          <t>ROS x Norman Zoom</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Sean Wildes</t>
+          <t>Max Kramer</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
+          <t>Religion of Sports</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>Scheduling/exec</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>swildes@proskauer.com</t>
+          <t>max.kramer@religionofsports.com</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Proskauer team</t>
+          <t>Set ROS Zoom</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Alex Miska</t>
+          <t>Todd Barrish</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Foley &amp; Lardner</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
+          <t>Religion of Sports</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr"/>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>amiska@foley.com</t>
+          <t>todd.barrish@religionofsports.com</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Foley team</t>
+          <t>ROS team</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3226,93 +3310,1735 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Legal — confirm engagement</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Trey McDonald</t>
+          <t>Joey Kravetz</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Foley &amp; Lardner</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
+          <t>Religion of Sports</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr"/>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>trey.mcdonald@foley.com</t>
+          <t>joey.kravetz@religionofsports.com</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Foley team</t>
+          <t>ROS team (Apr)</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
+          <t>Pietro Moro</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Religion of Sports</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>pietro@religionofsports.com</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>ROS team</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Team member</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Victoria Del Rossi</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Candle Studios (Candle Media)</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Exec</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>victoria.delrossi@candlestudios.com</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>May/June thread</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Warm — follow up</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>A. Schneider (confirm)</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Candle Studios</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Exec</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>aschneider@candlestudios.com</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Ongoing via Sunjay</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Josh (confirm surname)</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Straylight Productions</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>jtb@straylightprod.co</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Production decks + Becca edits</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Eric Newman</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>(own production company)</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Producer — angling for work; intro via Steve Donahue</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>coachenew@gmail.com</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Sent names list; SJU coach intro</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Active — confirm fit/role</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Geoff Chow</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>The Ringer / Spotify</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Media / press</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>geoff.chow@theringer.com</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Press angle (also geoffc@spotify.com)</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Warm — press</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Randy (confirm surname)</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Training Ground AI</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Tech / training</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>randy@trainingground.ai</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>June/July thread</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Confirm relevance</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Schools (ADs / Coaches / Staff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Steve Donahue</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Saint Joseph's (SJU)</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Head Men's Basketball Coach</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>sdonahue1@sju.edu</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>LOI signed; intro'd Eric Newman</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>LOI SIGNED — active</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Tracey Pachman</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Saint Joseph's (SJU)</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>General Counsel</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>tpachman@sju.edu</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>On SJU LOI/legal</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Ashwin Puri</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Saint Joseph's (SJU)</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>CFO — signed the LOI</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>apuri@sju.edu</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>LOI signed 7/29</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>LOI SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Joseph Mihalich</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Saint Joseph's (SJU)</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Athletics (confirm title)</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>jmihalich@sju.edu</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Primary SJU contact since June</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>F. Reynolds (confirm)</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Saint Joseph's (SJU)</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Marketing VP</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>freynolds@sju.edu</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>SJU marketing</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Contact as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>K. Welsh (confirm)</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Saint Joseph's (SJU)</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Marketing VP</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>kwelsh@sju.edu</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>SJU marketing</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Contact as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>E. Laudano (confirm)</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Saint Joseph's (SJU)</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Marketing VP</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>elaudano@sju.edu</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>SJU marketing</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Contact as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Chris Caputo</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>George Washington (GW)</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Head Men's Basketball Coach</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>coachcaputo@gwu.edu</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Championed to his AD</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Active — met 8/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Michael Lipitz</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>George Washington (GW)</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Athletic Director</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>michael.lipitz@email.gwu.edu</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Met 8/7</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Active — follow up</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Chris Clunie</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Athletic Director (confirm)</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>chclunie@davidson.edu</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Davidson (Curry flagship)</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Active — flagship school</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Nathan Davis</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>New Hampshire (UNH)</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Head Coach (confirm)</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>nathan.davis@unh.edu</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>LOI draft sent</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Active — LOI in play</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>J. Gallo (confirm)</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Merrimack</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title)</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>galloj@merrimack.edu</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Call Aug 19</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Active — call scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Seth Needle</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Temple</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title — mktg/AD)</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>seth.needle@temple.edu</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>May/June outreach</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Warm — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Daniel Lobacz</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Temple</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title)</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>daniel.lobacz@temple.edu</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>June outreach</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Warm — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Matthew Kingsley</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Yale</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title)</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>matthew.kingsley@yale.edu</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>June outreach</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Cold — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Tobe Carberry</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Yale</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title)</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>tobe.carberry@yale.edu</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>June outreach</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Cold — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Michael Martin</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title)</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>michael_martin@brown.edu</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>May (w/ T. Wheeler)</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Cold — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Tyson Wheeler</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Coach (confirm)</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>tyson_wheeler@brown.edu</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>May outreach</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Cold — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>W. Gibson (confirm)</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Coach (confirm)</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>gibsonw@hawaii.edu</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>July outreach</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Warm — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>T. Hammel (confirm)</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Fordham</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title)</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>thammel1@fordham.edu</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>May + Aug outreach</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Warm — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>M. Sotsky (confirm)</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Harvard</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title)</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>msotsky@fas.harvard.edu</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>July thread</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Cold — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Chris Herren</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>(former NBA / speaker)</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Talent / advocate</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>chris@chrisherren.com</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>'WtW meets hoops' pitch</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>Warm — follow up</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
           <t>Brian Socolow</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>Loeb &amp; Loeb</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>Lead counsel (NIL/structure) — from vault</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Lead counsel (NIL / structure)</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>bsocolow@loeb.com</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>Engaged per vault (not in this email set)</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>Engaged — confirm active</t>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Engaged; primary legal</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>Engaged — primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>John Kulback</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Loeb &amp; Loeb</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Attorney (w/ Socolow)</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>jkulback@loeb.com</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>On Loeb threads</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Engaged</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>L. Wiznitzer (confirm)</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Loeb &amp; Loeb</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>lwiznitzer@loeb.com</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>On Loeb threads</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Engaged</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Robert Freeman</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Proskauer Rose</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Attorney (lead contact)</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>rfreeman@proskauer.com</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Active May</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Confirm current status</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Grant Darwin</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Proskauer Rose</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>gdarwin@proskauer.com</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>Proskauer team</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Kyle Casazza</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Proskauer Rose</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>kcasazza@proskauer.com</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>Proskauer team</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Sean Wildes</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Proskauer Rose</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>swildes@proskauer.com</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Proskauer team</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Alex Miska</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Foley &amp; Lardner</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>amiska@foley.com</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>Foley team</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Legal — confirm engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Trey McDonald</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Foley &amp; Lardner</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>trey.mcdonald@foley.com</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Foley team</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Advisory / Academic / Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>R. Bogosian (confirm)</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Babson College</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Faculty / advisor (entrepreneurship)</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>rbogosian@babson.edu</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>w/ A. Gondal</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>A. Gondal (confirm)</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Babson College</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Advisor / student</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>agondal1@babson.edu</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Ongoing June/July</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>G. Randlett (confirm)</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Babson College</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>grandlett@babson.edu</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>May thread</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Brett (confirm surname)</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Bullet Pitch</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Pitch/deck vendor (confirm)</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>brett@bulletpitch.com</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>May thread</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>Vendor — confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>(confirm) oot</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Concert Stuff</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Music / events (confirm)</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>oot@concertstuff.com</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>Ongoing w/ Sunjay to Aug 12</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>Active — confirm identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Sofi Selig (confirm)</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>(confirm org)</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Connect</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>sofi.selig@gmail.com</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>One-off April</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>P.J. de Silva (confirm)</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>(family?)</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Personal contact</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>pjdesilva1@gmail.com</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Apr/May thread</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Confirm — likely personal/family</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
-  <mergeCells count="6">
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A48:G48"/>
+  <mergeCells count="7">
+    <mergeCell ref="A123:G123"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A113:G113"/>
+    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3324,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3395,7 +5121,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>LOI signed; celeb TBD (Hart channel active)</t>
+          <t>LOI signed; celeb TBD (Hart active)</t>
         </is>
       </c>
     </row>
@@ -3412,7 +5138,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Film hook (White Men Can't Jump)</t>
+          <t>Film hook (WMCJ)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3439,7 +5165,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Engaging (Affleck)</t>
+          <t>Engaging</t>
         </is>
       </c>
     </row>
@@ -3461,7 +5187,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>LOI in play</t>
+          <t>LOI in play (Sandler via Happy Madison)</t>
         </is>
       </c>
     </row>
@@ -3495,7 +5221,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Larry Bird, David Goggins, John Mellencamp</t>
+          <t>Larry Bird, David Goggins</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -3505,7 +5231,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>PMG roster (Bird, Goggins)</t>
+          <t>PMG roster</t>
         </is>
       </c>
     </row>
@@ -3517,7 +5243,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Scottie Pippen (+ Arkansas name: Clinton/Thornton)</t>
+          <t>Scottie Pippen (+ Clinton/Thornton)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -3539,7 +5265,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Walt 'Clyde' Frazier (+ Melissa McCarthy / Bob Odenkirk)</t>
+          <t>Walt 'Clyde' Frazier (+ McCarthy/Odenkirk)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3549,7 +5275,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>PMG (Frazier) — strong 2-alum pairing</t>
+          <t>PMG (Frazier) — strong pairing</t>
         </is>
       </c>
     </row>
@@ -3571,7 +5297,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>PMG roster (Erving) — Dr. J also Philly</t>
+          <t>PMG (Erving); Dr. J also Philly</t>
         </is>
       </c>
     </row>
@@ -3583,7 +5309,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Tim Hardaway (+ Glory Road legacy)</t>
+          <t>Tim Hardaway (+ Glory Road)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3600,83 +5326,83 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>UMKC</t>
+          <t>Furman</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Jason Sudeikis, Paul Rudd</t>
+          <t>Kevin Garnett</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>HS ~20 min away</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Shortlist</t>
+          <t>Idea (per email)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Dwayne Johnson, Bruno Mars, Jason Momoa</t>
+          <t>Steve Nash</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Verified alum</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Shortlist</t>
+          <t>Via CTRL / WME</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Steve Nash</t>
+          <t>Bill Murray (via son Luke, HC), Amy Poehler</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Verified alum</t>
+          <t>BC ties</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Shortlist</t>
+          <t>Fallen-giant track</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>Wake Forest</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Bill Murray (via son Luke, HC), Amy Poehler</t>
+          <t>Tim Duncan, Muggsy Bogues</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>BC ties</t>
+          <t>Verified Deacons</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3688,152 +5414,86 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Furman</t>
+          <t>NYU (D3)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Kevin Garnett</t>
+          <t>Adam Sandler, Billy Crystal, Spike Lee</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>HS ~20 min from campus</t>
+          <t>Verified Tisch alumni</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Idea (per email)</t>
+          <t>D3 track</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Ball State</t>
+          <t>Johns Hopkins (D3)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>David Letterman</t>
+          <t>Mike Bloomberg, Michael Phelps, Carmelo Anthony</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Alum + major donor</t>
+          <t>Alum/local</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Shortlist</t>
+          <t>D3 track</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Charleston</t>
+          <t>Ivy outreach</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Bill Murray, Danny McBride</t>
+          <t>Yale, Brown, Harvard staff contacted</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Murray co-owns RiverDogs</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Shortlist</t>
+          <t>Exploratory</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Wake Forest</t>
+          <t>Reps in motion</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Tim Duncan, Muggsy Bogues</t>
+          <t>Ludacris &amp; Tim McGraw (CAA); Brian Scalabrine (direct)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Verified Deacons</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Fallen-giant track</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>NYU (D3)</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Adam Sandler, Billy Crystal, Spike Lee</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Verified Tisch alumni</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>D3 track</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Johns Hopkins (D3)</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Mike Bloomberg, Michael Phelps, Carmelo Anthony</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Alum/local</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>D3 track</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Reps in motion (not school-specific)</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Ludacris &amp; Tim McGraw (via CAA/Gelbard)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Agent pass-through active</t>
         </is>

--- a/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
+++ b/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1584,49 +1584,49 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Marc Gottesman</t>
+          <t>'mags'</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
+          <t>Smash Sports</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Investor — likely your 'mags'</t>
+          <t>Investor — this is your 'mags'</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>marc.gottesman1@gmail.com</t>
+          <t>mags@smashsports.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>One-off outreach May</t>
+          <t>Cold outreach</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Confirm — 'mags'? revisit</t>
+          <t>Cold — revisit ('mags')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Chuck (confirm surname)</t>
+          <t>Marc Gottesman</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Winnie Capital</t>
+          <t>(confirm org)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1636,108 +1636,108 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>chuck@winniecap.com</t>
+          <t>marc.gottesman1@gmail.com</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>One-off outreach May</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Chip (confirm surname)</t>
+          <t>Ben Simon</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Eight State</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>Investor/banking</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>chip@eightstate.com</t>
+          <t>Ben.Simon@gs.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>w/ Elisa</t>
+          <t>Cold outreach</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Elisa (confirm surname)</t>
+          <t>Devon / Stephane</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Eight State</t>
+          <t>Stedde Capital</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>Investors</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>elisa@eightstate.com</t>
+          <t>devon@steddecapital.com</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Eight State team</t>
+          <t>Cold outreach</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Nathaniel (confirm surname)</t>
+          <t>Chuck (confirm surname)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>DGB.vc</t>
+          <t>Winnie Capital</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1747,17 +1747,17 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>nathaniel@dgb.vc</t>
+          <t>chuck@winniecap.com</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>One-off June</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -1769,12 +1769,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Adrian Williams</t>
+          <t>Chip (confirm surname)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>SC Holdings</t>
+          <t>Eight State</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1784,34 +1784,34 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>adrian@sc.holdings</t>
+          <t>chip@eightstate.com</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>On calendar</t>
+          <t>w/ Elisa</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Confirm status</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Eric (confirm surname)</t>
+          <t>Elisa (confirm surname)</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>VaynerWatt</t>
+          <t>Eight State</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>eric@vaynerwatt.com</t>
+          <t>elisa@eightstate.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>w/ Sam</t>
+          <t>Eight State team</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -1843,12 +1843,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Sam (confirm surname)</t>
+          <t>Nathaniel (confirm surname)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>VaynerWatt</t>
+          <t>DGB.vc</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1858,108 +1858,108 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>sam@vaynerwatt.com</t>
+          <t>nathaniel@dgb.vc</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>VaynerWatt team</t>
+          <t>One-off June</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Aaron (confirm surname)</t>
+          <t>Adrian Williams</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Paul Street</t>
+          <t>SC Holdings</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>On Hart/Just Train + investor calls</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>aaron@paulstreet.co</t>
+          <t>adrian@sc.holdings</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Recurring since May</t>
+          <t>On calendar</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Active — confirm role</t>
+          <t>Confirm status</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Eric Paredes</t>
+          <t>Eric (confirm surname)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>JP Morgan</t>
+          <t>VaynerWatt</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>eric.a.paredes@jpmorgan.com</t>
+          <t>eric@vaynerwatt.com</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Cinderella Corp thread</t>
+          <t>w/ Sam</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Confirm status</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Jordan (confirm surname)</t>
+          <t>Sam (confirm surname)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Cymbul</t>
+          <t>VaynerWatt</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1969,91 +1969,91 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>jordan@cymbul.co</t>
+          <t>sam@vaynerwatt.com</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>One-off May</t>
+          <t>VaynerWatt team</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Nate Fritsch</t>
+          <t>Aaron (confirm surname)</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Kaba AI</t>
+          <t>Paul Street</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Investor / advisor</t>
+          <t>On Hart/Just Train + investor calls</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>nate.fritsch@kaba.ai</t>
+          <t>aaron@paulstreet.co</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>One-off April</t>
+          <t>Recurring since May</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Active — confirm role</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Allen Cheng</t>
+          <t>Eric Paredes</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
+          <t>JP Morgan</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Investor / advisor</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>allen@allencheng.com</t>
+          <t>eric.a.paredes@jpmorgan.com</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>On calendar</t>
+          <t>Cinderella Corp thread</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2065,81 +2065,81 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Hunter Reinhart</t>
+          <t>Jordan (confirm surname)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
+          <t>Cymbul</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Meeting organizer</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>hunterreinhart@gmail.com</t>
+          <t>jordan@cymbul.co</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Set a meeting June</t>
+          <t>One-off May</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Jeremy Peschka</t>
+          <t>Nate Fritsch</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>(confirm org; House of Gambel?)</t>
+          <t>Kaba AI</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Investor / connect</t>
+          <t>Investor / advisor</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>jeremy.peschka@gmail.com</t>
+          <t>nate.fritsch@kaba.ai</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>w/ houseofgambel@gmail.com</t>
+          <t>One-off April</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Varun Sudhakar</t>
+          <t>Allen Cheng</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2149,96 +2149,96 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Investor / connect</t>
+          <t>Investor / advisor</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>varun.sudhakar13@gmail.com</t>
+          <t>allen@allencheng.com</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>June threads</t>
+          <t>On calendar</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Confirm status</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>(confirm) barwinca</t>
+          <t>Hunter Reinhart</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>(confirm) SJU-connected</t>
+          <t>(confirm org)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Intermediary w/ Saint Joseph's</t>
+          <t>Meeting organizer</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>barwinca@gmail.com</t>
+          <t>hunterreinhart@gmail.com</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Cc'd on SJU/Mihalich threads</t>
+          <t>Set a meeting June</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity (SJU booster?)</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>(confirm) ddilieg</t>
+          <t>Jeremy Peschka</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
+          <t>(confirm org; House of Gambel?)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Connect</t>
+          <t>Investor / connect</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>ddilieg@gmail.com</t>
+          <t>jeremy.peschka@gmail.com</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Starred back-and-forth July</t>
+          <t>w/ houseofgambel@gmail.com</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2250,400 +2250,400 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>David Famolari</t>
+          <t>Varun Sudhakar</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>(confirm org — Verizon Ventures?)</t>
+          <t>(confirm org)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Investor — YOU flagged, not found in email</t>
+          <t>Investor / connect</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>(confirm email)</t>
+          <t>varun.sudhakar13@gmail.com</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>You named as a VC to include</t>
+          <t>June threads</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Add — confirm contact info</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Celebrity Reps / Agents / Talent Camps</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>(confirm) barwinca</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>(confirm) SJU-connected</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Intermediary w/ Saint Joseph's</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>barwinca@gmail.com</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Cc'd on SJU/Mihalich threads</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Confirm identity (SJU booster?)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Darren Prince</t>
+          <t>(confirm) ddilieg</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Prince Marketing Group</t>
+          <t>(confirm org)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Founder/CEO — agent (Magic, Bird, Pippen, Goggins...)</t>
+          <t>Connect</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>dprince@princemarketinggroup.com</t>
+          <t>ddilieg@gmail.com</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Warm intro; handed to Mathilda</t>
+          <t>Starred back-and-forth July</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Mathilda Tennysdotter</t>
+          <t>David Famolari</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Prince Marketing Group</t>
+          <t>(confirm org — Verizon Ventures?)</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>COO, Talent Rep</t>
+          <t>Investor — YOU flagged, not found in email</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>mathilda@princemarketinggroup.com</t>
+          <t>(confirm email)</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Suggesting names; call offered</t>
+          <t>You named as a VC to include</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>HOT — awaiting names</t>
+          <t>Add — confirm contact info</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Kevin Gelbard</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>CAA</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Agent — Ludacris, Tim McGraw</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>kevin.gelbard@caa.com</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Passing to Luda &amp; Tim teams</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Active — awaiting pass-through</t>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Celebrity Reps / Agents / Talent Camps</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>David Sherman</t>
+          <t>Darren Prince</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>WME</t>
+          <t>Prince Marketing Group</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Non-scripted</t>
+          <t>Founder/CEO — agent (Magic, Bird, Pippen, Goggins...)</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>dsherman@wmeagency.com</t>
+          <t>dprince@princemarketinggroup.com</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Existing connection</t>
+          <t>Warm intro; handed to Mathilda</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Warm — reconnect</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>DJS (confirm name)</t>
+          <t>Mathilda Tennysdotter</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>WME</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr"/>
+          <t>Prince Marketing Group</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>COO, Talent Rep</t>
+        </is>
+      </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>djs@wmeagency.com</t>
+          <t>mathilda@princemarketinggroup.com</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>WME calendar invite</t>
+          <t>Suggesting names; call offered</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>HOT — awaiting names</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Erick Peyton</t>
+          <t>Kevin Gelbard</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Unanimous Media (Steph Curry)</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Exec — Curry/Davidson</t>
+          <t>Agent — Ludacris, Tim McGraw</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>erick@unanimousmedia.com</t>
+          <t>kevin.gelbard@caa.com</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Flagship pairing since May</t>
+          <t>Passing to Luda &amp; Tim teams</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Active — flagship</t>
+          <t>Active — awaiting pass-through</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Ron 'Boss' Everline</t>
+          <t>David Sherman</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Just Train / Hartbeat Ventures (Kevin Hart)</t>
+          <t>WME</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Principal — Hart camp</t>
+          <t>Non-scripted</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>boss@just-train.com</t>
+          <t>dsherman@wmeagency.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Hart -&gt; St. Joe's</t>
+          <t>Existing connection</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Active — Hart channel (also boss@hartbeatventures.com)</t>
+          <t>Warm — reconnect</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Kalani Jones</t>
+          <t>DJS (confirm name)</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Just Train</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Ops/scheduling (Hart camp)</t>
-        </is>
-      </c>
+          <t>WME</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr"/>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>kalani@just-train.com</t>
+          <t>djs@wmeagency.com</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Set Just Train Zooms</t>
+          <t>WME calendar invite</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Jay Jackson</t>
+          <t>Erick Peyton</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Humain Pro</t>
+          <t>Unanimous Media (Steph Curry)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Talent-side; 'Shane/Jay' outline</t>
+          <t>Exec — Curry/Davidson</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>jay@humainpro.com</t>
+          <t>erick@unanimousmedia.com</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Terms/alignment discussion</t>
+          <t>Flagship pairing since May</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active — flagship</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Shane Duffy</t>
+          <t>Ron 'Boss' Everline</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Humain Pro (confirm)</t>
+          <t>Just Train / Hartbeat Ventures (Kevin Hart)</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Talent-side; with Jay</t>
+          <t>Principal — Hart camp</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>seoda70@gmail.com</t>
+          <t>boss@just-train.com</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>'Shane/Jay'</t>
+          <t>Hart -&gt; St. Joe's</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -2653,335 +2653,335 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active — Hart channel (also boss@hartbeatventures.com)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Alan (confirm surname)</t>
+          <t>Kalani Jones</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>(w/ Humain — n9.lol)</t>
+          <t>Just Train</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Talent-side; on Shane/Jay thread</t>
+          <t>Ops/scheduling (Hart camp)</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>alan@n9.lol</t>
+          <t>kalani@just-train.com</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>cc on Humain thread</t>
+          <t>Set Just Train Zooms</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Jason Bernstein</t>
+          <t>Jay Jackson</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Clarity Football</t>
+          <t>Humain Pro</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Agent — Jason Kelce</t>
+          <t>Talent-side; 'Shane/Jay' outline</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>jason@clarityfootball.com</t>
+          <t>jay@humainpro.com</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Kelce deck (St. Joe's)</t>
+          <t>Terms/alignment discussion</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Active — Kelce</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Corey Smyth</t>
+          <t>Shane Duffy</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Blacksmith (NYC)</t>
+          <t>Humain Pro (confirm)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Manager/gatekeeper (Netflix + celeb access)</t>
+          <t>Talent-side; with Jay</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>csmyth@blacksmithnyc.com</t>
+          <t>seoda70@gmail.com</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>'Gatekeeper' per your note</t>
+          <t>'Shane/Jay'</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Active — sent deck</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Kristen (confirm surname)</t>
+          <t>Alan (confirm surname)</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Vanguard Sports Group</t>
+          <t>(w/ Humain — n9.lol)</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Talent-side; on Shane/Jay thread</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>kristen@vanguardsports.com</t>
+          <t>alan@n9.lol</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>April thread</t>
+          <t>cc on Humain thread</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit (also @vanguardsportsgroup.com)</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>E. Thomas (confirm)</t>
+          <t>Jason Bernstein</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Happy Madison (Adam Sandler)</t>
+          <t>Clarity Football</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Sandler's company</t>
+          <t>Agent — Jason Kelce</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>ethomas@happymadison.net</t>
+          <t>jason@clarityfootball.com</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Sandler channel (some bounced)</t>
+          <t>Kelce deck (St. Joe's)</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Cold — verify address</t>
+          <t>Active — Kelce</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Stephen (confirm surname)</t>
+          <t>Corey Smyth</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>Blacksmith (NYC)</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Rep — Steve Nash channel</t>
+          <t>Manager/gatekeeper (Netflix + celeb access)</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>ctrlstephen@gmail.com</t>
+          <t>csmyth@blacksmithnyc.com</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Nash via CTRL direct</t>
+          <t>'Gatekeeper' per your note</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Active — sent deck</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Alan Nierob</t>
+          <t>Kristen (confirm surname)</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Rogers &amp; Cowan PMK</t>
+          <t>Vanguard Sports Group</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Hollywood publicist</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>alan.nierob@rogersandcowanpmk.com</t>
+          <t>kristen@vanguardsports.com</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>One-off outreach May</t>
+          <t>April thread</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Cold — revisit (also @vanguardsportsgroup.com)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Brian Scalabrine</t>
+          <t>E. Thomas (confirm)</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>(former NBA / broadcaster)</t>
+          <t>Happy Madison (Adam Sandler)</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Talent / celebrity</t>
+          <t>Sandler's company</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>bscalabrine@yahoo.com</t>
+          <t>ethomas@happymadison.net</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Direct outreach June</t>
+          <t>Sandler channel (some bounced)</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Cold — verify address</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>G. Cheddy (confirm)</t>
+          <t>Stephen (confirm surname)</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>BEP-LA</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Talent/brand</t>
+          <t>Rep — Steve Nash channel</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>g.cheddy@bep-la.com</t>
+          <t>ctrlstephen@gmail.com</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Earliest outreach (Feb/Apr)</t>
+          <t>Nash via CTRL direct</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -2991,123 +2991,127 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Production / Streamers / Media</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Alan Nierob</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Rogers &amp; Cowan PMK</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Hollywood publicist</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>alan.nierob@rogersandcowanpmk.com</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>One-off outreach May</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Rebecca 'Becca' Gitlitz</t>
+          <t>Brian Scalabrine</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>EverWonder</t>
+          <t>(former NBA / broadcaster)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Production lead — deck edits</t>
+          <t>Talent / celebrity</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>rebecca.gitlitz@gmail.com</t>
+          <t>bscalabrine@yahoo.com</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Iterating production deck</t>
+          <t>Direct outreach June</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Active — lead partner</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Deirdre Fenton</t>
+          <t>G. Cheddy (confirm)</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>EverWonder</t>
+          <t>BEP-LA</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Exec — introduced EverWonder</t>
+          <t>Talent/brand</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>deirdre.a.fenton@gmail.com</t>
+          <t>g.cheddy@bep-la.com</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Since May</t>
+          <t>Earliest outreach (Feb/Apr)</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Clara Lawry</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>EverWonder</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>clara.lawry@everwonder.studio</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>EverWonder team</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>Team member</t>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Production / Streamers / Media</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Ian (confirm surname)</t>
+          <t>Rebecca 'Becca' Gitlitz</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3115,32 +3119,36 @@
           <t>EverWonder</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Production lead — deck edits</t>
+        </is>
+      </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>ian@everwonder.studio</t>
+          <t>rebecca.gitlitz@gmail.com</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>EverWonder team</t>
+          <t>Iterating production deck</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Active — lead partner</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Mike (confirm surname)</t>
+          <t>Deirdre Fenton</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3148,143 +3156,135 @@
           <t>EverWonder</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Exec — introduced EverWonder</t>
+        </is>
+      </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>mike@everwonder.studio</t>
+          <t>deirdre.a.fenton@gmail.com</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>EverWonder team</t>
+          <t>Since May</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Ameeth Sankaran (confirm)</t>
+          <t>Clara Lawry</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>Founder/exec</t>
-        </is>
-      </c>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr"/>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>ameeth@religionofsports.com</t>
+          <t>clara.lawry@everwonder.studio</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>ROS lead thread (Apr)</t>
+          <t>EverWonder team</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Jonathan Schaerf</t>
+          <t>Ian (confirm surname)</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>Exec</t>
-        </is>
-      </c>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr"/>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>jonathan@religionofsports.com</t>
+          <t>ian@everwonder.studio</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>ROS x Norman Zoom</t>
+          <t>EverWonder team</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Max Kramer</t>
+          <t>Mike (confirm surname)</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>Scheduling/exec</t>
-        </is>
-      </c>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr"/>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>max.kramer@religionofsports.com</t>
+          <t>mike@everwonder.studio</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Set ROS Zoom</t>
+          <t>EverWonder team</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Todd Barrish</t>
+          <t>Ameeth Sankaran (confirm)</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3292,32 +3292,36 @@
           <t>Religion of Sports</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Founder/exec</t>
+        </is>
+      </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>todd.barrish@religionofsports.com</t>
+          <t>ameeth@religionofsports.com</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>ROS team</t>
+          <t>ROS lead thread (Apr)</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Joey Kravetz</t>
+          <t>Jonathan Schaerf</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3325,32 +3329,36 @@
           <t>Religion of Sports</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr"/>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Exec</t>
+        </is>
+      </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>joey.kravetz@religionofsports.com</t>
+          <t>jonathan@religionofsports.com</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>ROS team (Apr)</t>
+          <t>ROS x Norman Zoom</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Pietro Moro</t>
+          <t>Max Kramer</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3358,372 +3366,364 @@
           <t>Religion of Sports</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Scheduling/exec</t>
+        </is>
+      </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>pietro@religionofsports.com</t>
+          <t>max.kramer@religionofsports.com</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>ROS team</t>
+          <t>Set ROS Zoom</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Victoria Del Rossi</t>
+          <t>Todd Barrish</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Candle Studios (Candle Media)</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>Exec</t>
-        </is>
-      </c>
+          <t>Religion of Sports</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr"/>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>victoria.delrossi@candlestudios.com</t>
+          <t>todd.barrish@religionofsports.com</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>May/June thread</t>
+          <t>ROS team</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>A. Schneider (confirm)</t>
+          <t>Joey Kravetz</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Candle Studios</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>Exec</t>
-        </is>
-      </c>
+          <t>Religion of Sports</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr"/>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>aschneider@candlestudios.com</t>
+          <t>joey.kravetz@religionofsports.com</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Ongoing via Sunjay</t>
+          <t>ROS team (Apr)</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Josh (confirm surname)</t>
+          <t>Pietro Moro</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Straylight Productions</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>Production</t>
-        </is>
-      </c>
+          <t>Religion of Sports</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr"/>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>jtb@straylightprod.co</t>
+          <t>pietro@religionofsports.com</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Production decks + Becca edits</t>
+          <t>ROS team</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Eric Newman</t>
+          <t>Victoria Del Rossi</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>(own production company)</t>
+          <t>Candle Studios (Candle Media)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Producer — angling for work; intro via Steve Donahue</t>
+          <t>Exec</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>coachenew@gmail.com</t>
+          <t>victoria.delrossi@candlestudios.com</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Sent names list; SJU coach intro</t>
+          <t>May/June thread</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Active — confirm fit/role</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Geoff Chow</t>
+          <t>A. Schneider (confirm)</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>The Ringer / Spotify</t>
+          <t>Candle Studios</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Media / press</t>
+          <t>Exec</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>geoff.chow@theringer.com</t>
+          <t>aschneider@candlestudios.com</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Press angle (also geoffc@spotify.com)</t>
+          <t>Ongoing via Sunjay</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Warm — press</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Randy (confirm surname)</t>
+          <t>Josh (confirm surname)</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Training Ground AI</t>
+          <t>Straylight Productions</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Tech / training</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>randy@trainingground.ai</t>
+          <t>jtb@straylightprod.co</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>June/July thread</t>
+          <t>Production decks + Becca edits</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Confirm relevance</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Schools (ADs / Coaches / Staff)</t>
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Eric Newman</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>(own production company)</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Producer — angling for work; intro via Steve Donahue</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>coachenew@gmail.com</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Sent names list; SJU coach intro</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Active — confirm fit/role</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Steve Donahue</t>
+          <t>Geoff Chow</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's (SJU)</t>
+          <t>The Ringer / Spotify</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Head Men's Basketball Coach</t>
+          <t>Media / press</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>sdonahue1@sju.edu</t>
+          <t>geoff.chow@theringer.com</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>LOI signed; intro'd Eric Newman</t>
+          <t>Press angle (also geoffc@spotify.com)</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>LOI SIGNED — active</t>
+          <t>Warm — press</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Tracey Pachman</t>
+          <t>Randy (confirm surname)</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's (SJU)</t>
+          <t>Training Ground AI</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>General Counsel</t>
+          <t>Tech / training</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>tpachman@sju.edu</t>
+          <t>randy@trainingground.ai</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>On SJU LOI/legal</t>
+          <t>June/July thread</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Confirm relevance</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>Ashwin Puri</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>Saint Joseph's (SJU)</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>CFO — signed the LOI</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>apuri@sju.edu</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>LOI signed 7/29</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>LOI SIGNED</t>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Schools (ADs / Coaches / Staff)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Joseph Mihalich</t>
+          <t>Steve Donahue</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3733,34 +3733,34 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Athletics (confirm title)</t>
+          <t>Head Men's Basketball Coach</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>jmihalich@sju.edu</t>
+          <t>sdonahue1@sju.edu</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Primary SJU contact since June</t>
+          <t>LOI signed; intro'd Eric Newman</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>LOI SIGNED — active</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>F. Reynolds (confirm)</t>
+          <t>Tracey Pachman</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3770,17 +3770,17 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Marketing VP</t>
+          <t>General Counsel</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>freynolds@sju.edu</t>
+          <t>tpachman@sju.edu</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>SJU marketing</t>
+          <t>On SJU LOI/legal</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -3790,14 +3790,14 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Contact as needed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>K. Welsh (confirm)</t>
+          <t>Ashwin Puri</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3807,34 +3807,34 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Marketing VP</t>
+          <t>CFO — signed the LOI</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>kwelsh@sju.edu</t>
+          <t>apuri@sju.edu</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>SJU marketing</t>
+          <t>LOI signed 7/29</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>Contact as needed</t>
+          <t>LOI SIGNED</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>E. Laudano (confirm)</t>
+          <t>Joseph Mihalich</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3844,128 +3844,128 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Marketing VP</t>
+          <t>Athletics (confirm title)</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>elaudano@sju.edu</t>
+          <t>jmihalich@sju.edu</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>SJU marketing</t>
+          <t>Primary SJU contact since June</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Contact as needed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Chris Caputo</t>
+          <t>F. Reynolds (confirm)</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>George Washington (GW)</t>
+          <t>Saint Joseph's (SJU)</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Head Men's Basketball Coach</t>
+          <t>Marketing VP</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>coachcaputo@gwu.edu</t>
+          <t>freynolds@sju.edu</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Championed to his AD</t>
+          <t>SJU marketing</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>Active — met 8/7</t>
+          <t>Contact as needed</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Michael Lipitz</t>
+          <t>K. Welsh (confirm)</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>George Washington (GW)</t>
+          <t>Saint Joseph's (SJU)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Athletic Director</t>
+          <t>Marketing VP</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>michael.lipitz@email.gwu.edu</t>
+          <t>kwelsh@sju.edu</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Met 8/7</t>
+          <t>SJU marketing</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>Active — follow up</t>
+          <t>Contact as needed</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Chris Clunie</t>
+          <t>E. Laudano (confirm)</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Saint Joseph's (SJU)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Athletic Director (confirm)</t>
+          <t>Marketing VP</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>chclunie@davidson.edu</t>
+          <t>elaudano@sju.edu</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Davidson (Curry flagship)</t>
+          <t>SJU marketing</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -3975,167 +3975,167 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Active — flagship school</t>
+          <t>Contact as needed</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Nathan Davis</t>
+          <t>Chris Caputo</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>New Hampshire (UNH)</t>
+          <t>George Washington (GW)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Head Coach (confirm)</t>
+          <t>Head Men's Basketball Coach</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>nathan.davis@unh.edu</t>
+          <t>coachcaputo@gwu.edu</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>LOI draft sent</t>
+          <t>Championed to his AD</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Active — LOI in play</t>
+          <t>Active — met 8/7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>J. Gallo (confirm)</t>
+          <t>Michael Lipitz</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Merrimack</t>
+          <t>George Washington (GW)</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>Athletic Director</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>galloj@merrimack.edu</t>
+          <t>michael.lipitz@email.gwu.edu</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Call Aug 19</t>
+          <t>Met 8/7</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>Active — call scheduled</t>
+          <t>Active — follow up</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Seth Needle</t>
+          <t>Chris Clunie</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Temple</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>(confirm title — mktg/AD)</t>
+          <t>Athletic Director (confirm)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>seth.needle@temple.edu</t>
+          <t>chclunie@davidson.edu</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>May/June outreach</t>
+          <t>Davidson (Curry flagship)</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>Warm — revisit</t>
+          <t>Active — flagship school</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Daniel Lobacz</t>
+          <t>Nathan Davis</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Temple</t>
+          <t>New Hampshire (UNH)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>Head Coach (confirm)</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>daniel.lobacz@temple.edu</t>
+          <t>nathan.davis@unh.edu</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>June outreach</t>
+          <t>LOI draft sent</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Warm — revisit</t>
+          <t>Active — LOI in play</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Matthew Kingsley</t>
+          <t>J. Gallo (confirm)</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4145,71 +4145,71 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>matthew.kingsley@yale.edu</t>
+          <t>galloj@merrimack.edu</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>June outreach</t>
+          <t>Call Aug 19</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Active — call scheduled</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Tobe Carberry</t>
+          <t>Seth Needle</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>Temple</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>(confirm title — mktg/AD)</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>tobe.carberry@yale.edu</t>
+          <t>seth.needle@temple.edu</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>June outreach</t>
+          <t>May/June outreach</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Warm — revisit</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Michael Martin</t>
+          <t>Daniel Lobacz</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Temple</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -4219,54 +4219,54 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>michael_martin@brown.edu</t>
+          <t>daniel.lobacz@temple.edu</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>May (w/ T. Wheeler)</t>
+          <t>June outreach</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Warm — revisit</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Tyson Wheeler</t>
+          <t>Matthew Kingsley</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Coach (confirm)</t>
+          <t>(confirm title)</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>tyson_wheeler@brown.edu</t>
+          <t>matthew.kingsley@yale.edu</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>May outreach</t>
+          <t>June outreach</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -4278,49 +4278,49 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>W. Gibson (confirm)</t>
+          <t>Tobe Carberry</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Coach (confirm)</t>
+          <t>(confirm title)</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>gibsonw@hawaii.edu</t>
+          <t>tobe.carberry@yale.edu</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>July outreach</t>
+          <t>June outreach</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Warm — revisit</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>T. Hammel (confirm)</t>
+          <t>Michael Martin</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4330,54 +4330,54 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>thammel1@fordham.edu</t>
+          <t>michael_martin@brown.edu</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>May + Aug outreach</t>
+          <t>May (w/ T. Wheeler)</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>Warm — revisit</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>M. Sotsky (confirm)</t>
+          <t>Tyson Wheeler</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Harvard</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>Coach (confirm)</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>msotsky@fas.harvard.edu</t>
+          <t>tyson_wheeler@brown.edu</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>July thread</t>
+          <t>May outreach</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -4389,241 +4389,241 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Chris Herren</t>
+          <t>W. Gibson (confirm)</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>(former NBA / speaker)</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Talent / advocate</t>
+          <t>Coach (confirm)</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>chris@chrisherren.com</t>
+          <t>gibsonw@hawaii.edu</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>'WtW meets hoops' pitch</t>
+          <t>July outreach</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Warm — revisit</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Legal</t>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>T. Hammel (confirm)</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Fordham</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title)</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>thammel1@fordham.edu</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>May + Aug outreach</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Warm — revisit</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Brian Socolow</t>
+          <t>M. Sotsky (confirm)</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Loeb &amp; Loeb</t>
+          <t>Harvard</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Lead counsel (NIL / structure)</t>
+          <t>(confirm title)</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>bsocolow@loeb.com</t>
+          <t>msotsky@fas.harvard.edu</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Engaged; primary legal</t>
+          <t>July thread</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>Engaged — primary</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>John Kulback</t>
+          <t>Chris Herren</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Loeb &amp; Loeb</t>
+          <t>(former NBA / speaker)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Attorney (w/ Socolow)</t>
+          <t>Talent / advocate</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>jkulback@loeb.com</t>
+          <t>chris@chrisherren.com</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>On Loeb threads</t>
+          <t>'WtW meets hoops' pitch</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>Engaged</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>L. Wiznitzer (confirm)</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Loeb &amp; Loeb</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>lwiznitzer@loeb.com</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>On Loeb threads</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>Engaged</t>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Robert Freeman</t>
+          <t>Brian Socolow</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
+          <t>Loeb &amp; Loeb</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Attorney (lead contact)</t>
+          <t>Lead counsel (NIL / structure)</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>rfreeman@proskauer.com</t>
+          <t>bsocolow@loeb.com</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Active May</t>
+          <t>Engaged; primary legal</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>Confirm current status</t>
+          <t>Engaged — primary</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Grant Darwin</t>
+          <t>John Kulback</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
+          <t>Loeb &amp; Loeb</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>Attorney (w/ Socolow)</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>gdarwin@proskauer.com</t>
+          <t>jkulback@loeb.com</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Proskauer team</t>
+          <t>On Loeb threads</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Kyle Casazza</t>
+          <t>L. Wiznitzer (confirm)</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
+          <t>Loeb &amp; Loeb</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -4633,29 +4633,29 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>kcasazza@proskauer.com</t>
+          <t>lwiznitzer@loeb.com</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Proskauer team</t>
+          <t>On Loeb threads</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Sean Wildes</t>
+          <t>Robert Freeman</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4665,39 +4665,39 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>Attorney (lead contact)</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>swildes@proskauer.com</t>
+          <t>rfreeman@proskauer.com</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Proskauer team</t>
+          <t>Active May</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Confirm current status</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Alex Miska</t>
+          <t>Grant Darwin</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Foley &amp; Lardner</t>
+          <t>Proskauer Rose</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>amiska@foley.com</t>
+          <t>gdarwin@proskauer.com</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Foley team</t>
+          <t>Proskauer team</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -4722,19 +4722,19 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Legal — confirm engagement</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Trey McDonald</t>
+          <t>Kyle Casazza</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Foley &amp; Lardner</t>
+          <t>Proskauer Rose</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>trey.mcdonald@foley.com</t>
+          <t>kcasazza@proskauer.com</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Foley team</t>
+          <t>Proskauer team</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -4764,281 +4764,2028 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Advisory / Academic / Other</t>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Sean Wildes</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Proskauer Rose</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>swildes@proskauer.com</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Proskauer team</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>R. Bogosian (confirm)</t>
+          <t>Alex Miska</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Babson College</t>
+          <t>Foley &amp; Lardner</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Faculty / advisor (entrepreneurship)</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>rbogosian@babson.edu</t>
+          <t>amiska@foley.com</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>w/ A. Gondal</t>
+          <t>Foley team</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Legal — confirm engagement</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>A. Gondal (confirm)</t>
+          <t>Trey McDonald</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Babson College</t>
+          <t>Foley &amp; Lardner</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Advisor / student</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>agondal1@babson.edu</t>
+          <t>trey.mcdonald@foley.com</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Ongoing June/July</t>
+          <t>Foley team</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>G. Randlett (confirm)</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>Babson College</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>Advisor</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>grandlett@babson.edu</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>May thread</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>Advisory</t>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Advisory / Academic / Other</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Brett (confirm surname)</t>
+          <t>R. Bogosian (confirm)</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Bullet Pitch</t>
+          <t>Babson College</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Pitch/deck vendor (confirm)</t>
+          <t>Faculty / advisor (entrepreneurship)</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>brett@bulletpitch.com</t>
+          <t>rbogosian@babson.edu</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>May thread</t>
+          <t>w/ A. Gondal</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>Vendor — confirm</t>
+          <t>Advisory</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>(confirm) oot</t>
+          <t>A. Gondal (confirm)</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Concert Stuff</t>
+          <t>Babson College</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Music / events (confirm)</t>
+          <t>Advisor / student</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>oot@concertstuff.com</t>
+          <t>agondal1@babson.edu</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Ongoing w/ Sunjay to Aug 12</t>
+          <t>Ongoing June/July</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>Active — confirm identity</t>
+          <t>Advisory</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Sofi Selig (confirm)</t>
+          <t>G. Randlett (confirm)</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
+          <t>Babson College</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Connect</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>sofi.selig@gmail.com</t>
+          <t>grandlett@babson.edu</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>One-off April</t>
+          <t>May thread</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Advisory</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
+          <t>Brett (confirm surname)</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Bullet Pitch</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Pitch/deck vendor (confirm)</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>brett@bulletpitch.com</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>May thread</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Vendor — confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>(confirm) oot</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Concert Stuff</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Music / events (confirm)</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>oot@concertstuff.com</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Ongoing w/ Sunjay to Aug 12</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Active — confirm identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Sofi Selig (confirm)</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>(confirm org)</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Connect</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>sofi.selig@gmail.com</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>One-off April</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
           <t>P.J. de Silva (confirm)</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>(family?)</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>Personal contact</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>pjdesilva1@gmail.com</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>Apr/May thread</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="G130" s="3" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>Confirm — likely personal/family</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Cold Outreach — Prospecting (Jan–Mar 2026 blast; firm-level, little/no response unless noted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>RedBird Capital</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Sports PE</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>B. Snow, K. Laforce</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>BSnow@redbirdcap.com</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 cold blast (note: RedBird now in active talks per vault)</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>Cold touch → see vault</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>TPG</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>J. Coulter, T. Sisitsky, J. Evans</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>jcoulter@tpg.com</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Avenue Capital</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Marc Lasry, J. Greenbaum, T. Marcy, S. Chimento</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>mlasry@avenuecapital.com</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Weatherford Capital</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Sports PE</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Will Weatherford</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Will@weatherfordcapital.com</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast (also does college-sports PE)</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Seventy Six Capital</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Sports VC</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>W. Kimmel, Scott</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>scott@seventysixcapital.com</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Elysian Park Ventures</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Sports VC (Dodgers)</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Pete, Cole</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>pete@elysianpark.ventures</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Advantage / AV.VC</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Sports VC</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Sam, Jeremy; Keaton, Greg</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>sam@advantage.vc</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Ryan Sports Ventures</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Sports VC</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>rob@ryansportsventures.com</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>TGR / TMRW Sports</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Sports (Tiger Woods)</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Rob, Glenn; info</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>glenn@tgr.ventures</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>359 Capital</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Doug, Michael</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>doug@359capital.com</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Chiron Sports Group</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>sam@chironsportsgroup.com</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 (bounced)</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>Bounced</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Apex Capital Partners</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Koen Bosma</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>koen.bosma@apex-cp.com</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Jan 19 blast</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Ludis Capital</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Sports VC</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Sam, Matilda, Chris</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>chris@ludis.capital</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Clearlake Capital</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Sports PE</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Todd Boehly, Tony Rosa, D. Groen</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>tboehly@clearlake.com</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit (Boehly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Haslam Sports Group</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Sports (Browns)</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Dee Haslam, D. Jenkins</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>deehaslam@haslamsports.com</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Thrive Capital</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>VC (Josh Kushner)</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Kareem, Joshua</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>joshua@thrivecap.com</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Benchmark</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Peter, Bill</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>peter@benchmark.com</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>NFX</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Pete, Gigi, James</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>gigi@nfx.com</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>General Atlantic</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>A. Crisses</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>acrisses@generalatlantic.com</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Konvoy VC</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Sports/gaming VC</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Jackson, Jason, Josh</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>jason@konvoy.vc</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Founder Collective</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>David, Eric, Micah</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>eric@foundercollective.com</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>Stripes</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Chris, Aidan, Ken</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>ken@stripes.co</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Sharp Alpha Advisors</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Sports VC</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Lloyd Danzig</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>lloyd@sharpalphaadvisors.com</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>GMF Capital</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Denney, Doug</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>doug@gmfcapital.com</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>IPR.VC</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Media fund</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Andrea, Timo</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>timo@ipr.vc</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Boardroom</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>Media (Rich Kleiman/Durant)</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Rich</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>rich@boardroom.tv</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Alpaca VC</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>david@alpaca.vc</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Candle Media</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Studio (Mayer &amp; Staggs)</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Mayer, Tom Staggs</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>kevin@candlemedia.com</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>No response — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Fifth Season</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Studio</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>L. Zimmermann, M. Lisio, K. Calabrese</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>mlisio@fifthseason.com</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Pulse Films</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Mino Jarjoura</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>mino.jarjoura@pulsefilms.com</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Mar 9 blast</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Bryan Lourd, Rick Kurtzman, Ethan Kurtzman, C. Carino, J. Darmody, J. MacGregor, T. Brennan</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>blourd@caa.com</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Feb 15+ agency blast</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>Mostly no response — a few opens</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>WME Entertainment</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>B. Slater, T. Curtis, D. Greenberg, H. Reisch, J. Lesh, N. Towne, S. Mark, W. Lowery, +</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>bslater@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Feb 14-16 blast</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>M. Jasper (+assistant), M. Berkowitz, S. Rabinowitz</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>mberkowitz@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>Feb-Mar blast</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>M. Jasper RESPONDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>United Talent (UTA)</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>K. Volchok, J. Barber, N. Gates, B. Lazarus, D. Duchon, K. Lubeck, J. Lawson, S. Sacks, +</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>volchokk@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>Feb 14-16 blast</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>K. Volchok RESPONDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Range Media Partners</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Mgmt/agency</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Hussey (Casey Affleck's mgr), Dave Bugliari, P. Orr, A. Glasgow, R. Astphan</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>khussey@rangemp.com</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>Feb 14 blast</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED (Hussey/Glasgow) — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>Octagon</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>Sports agency</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Jeff Austin</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>jeff.austin@octagon.com</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Feb 16 blast</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Untitled Entertainment</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>Mgmt</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>P. Murray</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>pmurray@untitledent.com</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>Feb 15 blast</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Independent Artists Media</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Mgmt</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Dave, Alex</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>dave@independentartistsmedia.com</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>Feb 14 blast</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Red Light Management</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Music mgmt</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Coran Capshaw</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>coran.capshaw@redlightmanagement.com</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>Feb 15 blast</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>EB Media PR</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Joseph, Ebie</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>ebie@ebmediapr.com</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>Feb 16 blast</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>Other mgmt/PR (Feb blast)</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Mgmt/PR</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Kipperman, The AMG, Montag Group, Neal Agency, TCC, KP Ent, Make Wake, Yumkas, CSC Biz Mgmt, Price Mgmt, Rowe PR, Rogers&amp;Cowan (Nierob), Leverage, Media4Mgmt, LB Ent</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>(various)</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>Feb 15 blast — see raw list</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>Mostly no response</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Schulz (camp)</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Comedian/talent</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Andrew, Dov, Tanya</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>andrew@theandrewschulz.com</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>Cold outreach</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>Cold — comedian target</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>Schools — additional cold</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>College AD/coach</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Holy Cross (Johnson/Paulsen/Rawlings), Stonehill (Kraus), UMBC (Lawson), Loyola (Blue), Coll. of Charleston (Harriman), Northeastern (Janning), BU (Quinn), UPenn</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>(various .edu)</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Aug outreach</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>Mixed — BU responded; rest cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>O'Melveny &amp; Myers</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Law firm</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Aronson, Reinstein, Afner</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>baronson@omm.com</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>Cold outreach</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
-  <mergeCells count="7">
-    <mergeCell ref="A123:G123"/>
+  <mergeCells count="8">
+    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="A116:G116"/>
+    <mergeCell ref="A126:G126"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A113:G113"/>
-    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A134:G134"/>
     <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
+++ b/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2287,17 +2287,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>(confirm) barwinca</t>
+          <t>Connor Barwin</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>(confirm) SJU-connected</t>
+          <t>Saint Joseph's (SJU-side connect)</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Intermediary w/ Saint Joseph's</t>
+          <t>Former NFL/Eagles; SJU liaison intro'd by Mihalich/Donahue</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Cc'd on SJU/Mihalich threads</t>
+          <t>SJU intro + early-July meeting</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity (SJU booster?)</t>
+          <t>Active — SJU connect</t>
         </is>
       </c>
     </row>
@@ -2516,742 +2516,750 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>David Sherman</t>
+          <t>Peter Hess</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>WME</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Non-scripted</t>
+          <t>Agent — reps Colin Jost, Jamie Foxx, Miles Teller, Bradley Cooper, Jason Bateman, Jimmy Fallon, Trace Adkins, Billy Crystal</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>dsherman@wmeagency.com</t>
+          <t>peter.hess@caa.com</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Existing connection</t>
+          <t>Multiple calls Mar 2026; offers made (Colin Jost etc). Asst: peter.hessasst@caa.com</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Warm — reconnect</t>
+          <t>WARM — Mar offers outstanding; revisit</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>DJS (confirm name)</t>
+          <t>Carla Laur</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>WME</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr"/>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Agent — Miles Teller, Walton Goggins</t>
+        </is>
+      </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>djs@wmeagency.com</t>
+          <t>claur@caa.com</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>WME calendar invite</t>
+          <t>Calls Mar 2026 re Teller/Goggins. Asst: Kathryn Powell (claurasst@caa.com)</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>WARM — Mar offers; revisit</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Erick Peyton</t>
+          <t>Rick Lucas</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Unanimous Media (Steph Curry)</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Exec — Curry/Davidson</t>
+          <t>Agent — Jamie Foxx</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>erick@unanimousmedia.com</t>
+          <t>rlucas@caa.com</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Flagship pairing since May</t>
+          <t>Jamie Foxx proposal Mar; referred to Adam Nettler. Asst: rlucasasst@caa.com</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Active — flagship</t>
+          <t>WARM — revisit</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Ron 'Boss' Everline</t>
+          <t>Adam Nettler</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Just Train / Hartbeat Ventures (Kevin Hart)</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Principal — Hart camp</t>
+          <t>Unscripted TV division</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>boss@just-train.com</t>
+          <t>adam.nettler@caa.com</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Hart -&gt; St. Joe's</t>
+          <t>Rick Lucas intro'd as better fit for the TV play</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Active — Hart channel (also boss@hartbeatventures.com)</t>
+          <t>WARM — the TV-side CAA contact</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Kalani Jones</t>
+          <t>David Sherman</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Just Train</t>
+          <t>WME</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Ops/scheduling (Hart camp)</t>
+          <t>Non-scripted</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>kalani@just-train.com</t>
+          <t>dsherman@wmeagency.com</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Set Just Train Zooms</t>
+          <t>Existing connection</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Warm — reconnect</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Jay Jackson</t>
+          <t>DJS (confirm name)</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Humain Pro</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Talent-side; 'Shane/Jay' outline</t>
-        </is>
-      </c>
+          <t>WME</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr"/>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>jay@humainpro.com</t>
+          <t>djs@wmeagency.com</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Terms/alignment discussion</t>
+          <t>WME calendar invite</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Shane Duffy</t>
+          <t>Erick Peyton</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Humain Pro (confirm)</t>
+          <t>Unanimous Media (Steph Curry)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Talent-side; with Jay</t>
+          <t>Exec — Curry/Davidson</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>seoda70@gmail.com</t>
+          <t>erick@unanimousmedia.com</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>'Shane/Jay'</t>
+          <t>Flagship pairing since May</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active — flagship</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Alan (confirm surname)</t>
+          <t>Ron 'Boss' Everline</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>(w/ Humain — n9.lol)</t>
+          <t>Just Train / Hartbeat Ventures (Kevin Hart)</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Talent-side; on Shane/Jay thread</t>
+          <t>Principal — Hart camp</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>alan@n9.lol</t>
+          <t>boss@just-train.com</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>cc on Humain thread</t>
+          <t>Hart -&gt; St. Joe's</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Active — Hart channel (also boss@hartbeatventures.com)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Jason Bernstein</t>
+          <t>Kalani Jones</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Clarity Football</t>
+          <t>Just Train</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Agent — Jason Kelce</t>
+          <t>Ops/scheduling (Hart camp)</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>jason@clarityfootball.com</t>
+          <t>kalani@just-train.com</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Kelce deck (St. Joe's)</t>
+          <t>Set Just Train Zooms</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Active — Kelce</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Corey Smyth</t>
+          <t>Jay Jackson</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Blacksmith (NYC)</t>
+          <t>Humain Pro</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Manager/gatekeeper (Netflix + celeb access)</t>
+          <t>Talent-side; 'Shane/Jay' outline</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>csmyth@blacksmithnyc.com</t>
+          <t>jay@humainpro.com</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>'Gatekeeper' per your note</t>
+          <t>Terms/alignment discussion</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Active — sent deck</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Kristen (confirm surname)</t>
+          <t>Shane Duffy</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Vanguard Sports Group</t>
+          <t>Humain Pro (confirm)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Talent-side; with Jay</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>kristen@vanguardsports.com</t>
+          <t>seoda70@gmail.com</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>April thread</t>
+          <t>'Shane/Jay'</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit (also @vanguardsportsgroup.com)</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>E. Thomas (confirm)</t>
+          <t>Alan (confirm surname)</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Happy Madison (Adam Sandler)</t>
+          <t>(w/ Humain — n9.lol)</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Sandler's company</t>
+          <t>Talent-side; on Shane/Jay thread</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>ethomas@happymadison.net</t>
+          <t>alan@n9.lol</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Sandler channel (some bounced)</t>
+          <t>cc on Humain thread</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Cold — verify address</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Stephen (confirm surname)</t>
+          <t>Jason Bernstein</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>Clarity Football</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Rep — Steve Nash channel</t>
+          <t>Agent — Jason Kelce</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>ctrlstephen@gmail.com</t>
+          <t>jason@clarityfootball.com</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Nash via CTRL direct</t>
+          <t>Kelce deck (St. Joe's)</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Active — Kelce</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Alan Nierob</t>
+          <t>Corey Smyth</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Rogers &amp; Cowan PMK</t>
+          <t>Blacksmith (NYC)</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Hollywood publicist</t>
+          <t>Manager/gatekeeper (Netflix + celeb access)</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>alan.nierob@rogersandcowanpmk.com</t>
+          <t>csmyth@blacksmithnyc.com</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>One-off outreach May</t>
+          <t>'Gatekeeper' per your note</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Active — sent deck</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Brian Scalabrine</t>
+          <t>Kristen (confirm surname)</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>(former NBA / broadcaster)</t>
+          <t>Vanguard Sports Group</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Talent / celebrity</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>bscalabrine@yahoo.com</t>
+          <t>kristen@vanguardsports.com</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Direct outreach June</t>
+          <t>April thread</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Cold — revisit (also @vanguardsportsgroup.com)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>G. Cheddy (confirm)</t>
+          <t>E. Thomas (confirm)</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>BEP-LA</t>
+          <t>Happy Madison (Adam Sandler)</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Talent/brand</t>
+          <t>Sandler's company</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>g.cheddy@bep-la.com</t>
+          <t>ethomas@happymadison.net</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Earliest outreach (Feb/Apr)</t>
+          <t>Sandler channel (some bounced)</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
+          <t>Cold — verify address</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Stephen (confirm surname)</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Rep — Steve Nash channel</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>ctrlstephen@gmail.com</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Nash via CTRL direct</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
           <t>Cold — revisit</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Production / Streamers / Media</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Rebecca 'Becca' Gitlitz</t>
+          <t>Alan Nierob</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>EverWonder</t>
+          <t>Rogers &amp; Cowan PMK</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Production lead — deck edits</t>
+          <t>Hollywood publicist</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>rebecca.gitlitz@gmail.com</t>
+          <t>alan.nierob@rogersandcowanpmk.com</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Iterating production deck</t>
+          <t>One-off outreach May</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Active — lead partner</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Deirdre Fenton</t>
+          <t>Brian Scalabrine</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>EverWonder</t>
+          <t>(former NBA / broadcaster)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Exec — introduced EverWonder</t>
+          <t>Talent / celebrity</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>deirdre.a.fenton@gmail.com</t>
+          <t>bscalabrine@yahoo.com</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Since May</t>
+          <t>Direct outreach June</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Clara Lawry</t>
+          <t>G. Cheddy (confirm)</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>EverWonder</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr"/>
+          <t>BEP-LA</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Talent/brand</t>
+        </is>
+      </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>clara.lawry@everwonder.studio</t>
+          <t>g.cheddy@bep-la.com</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>EverWonder team</t>
+          <t>Earliest outreach (Feb/Apr)</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>Ian (confirm surname)</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>EverWonder</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr"/>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>ian@everwonder.studio</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>EverWonder team</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>Team member</t>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Production / Streamers / Media</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Mike (confirm surname)</t>
+          <t>Rebecca 'Becca' Gitlitz</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3259,164 +3267,160 @@
           <t>EverWonder</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr"/>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Production lead — deck edits</t>
+        </is>
+      </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>mike@everwonder.studio</t>
+          <t>rebecca.gitlitz@gmail.com</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>EverWonder team</t>
+          <t>Iterating production deck</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Active — lead partner</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Ameeth Sankaran (confirm)</t>
+          <t>Deirdre Fenton</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
+          <t>EverWonder</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Founder/exec</t>
+          <t>Exec — introduced EverWonder</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>ameeth@religionofsports.com</t>
+          <t>deirdre.a.fenton@gmail.com</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>ROS lead thread (Apr)</t>
+          <t>Since May</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Jonathan Schaerf</t>
+          <t>Clara Lawry</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>Exec</t>
-        </is>
-      </c>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr"/>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>jonathan@religionofsports.com</t>
+          <t>clara.lawry@everwonder.studio</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>ROS x Norman Zoom</t>
+          <t>EverWonder team</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Max Kramer</t>
+          <t>Ian (confirm surname)</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>Scheduling/exec</t>
-        </is>
-      </c>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr"/>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>max.kramer@religionofsports.com</t>
+          <t>ian@everwonder.studio</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Set ROS Zoom</t>
+          <t>EverWonder team</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Todd Barrish</t>
+          <t>Mike (confirm surname)</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Religion of Sports</t>
+          <t>EverWonder</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr"/>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>todd.barrish@religionofsports.com</t>
+          <t>mike@everwonder.studio</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>ROS team</t>
+          <t>EverWonder team</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -3428,7 +3432,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Joey Kravetz</t>
+          <t>Ameeth Sankaran (confirm)</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3436,32 +3440,36 @@
           <t>Religion of Sports</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr"/>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Founder/exec</t>
+        </is>
+      </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>joey.kravetz@religionofsports.com</t>
+          <t>ameeth@religionofsports.com</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>ROS team (Apr)</t>
+          <t>ROS lead thread (Apr)</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Pietro Moro</t>
+          <t>Jonathan Schaerf</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3469,409 +3477,401 @@
           <t>Religion of Sports</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Exec</t>
+        </is>
+      </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>pietro@religionofsports.com</t>
+          <t>jonathan@religionofsports.com</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>ROS team</t>
+          <t>ROS x Norman Zoom</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Team member</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Victoria Del Rossi</t>
+          <t>Max Kramer</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Candle Studios (Candle Media)</t>
+          <t>Religion of Sports</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Exec</t>
+          <t>Scheduling/exec</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>victoria.delrossi@candlestudios.com</t>
+          <t>max.kramer@religionofsports.com</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>May/June thread</t>
+          <t>Set ROS Zoom</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>A. Schneider (confirm)</t>
+          <t>Todd Barrish</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Candle Studios</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>Exec</t>
-        </is>
-      </c>
+          <t>Religion of Sports</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr"/>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>aschneider@candlestudios.com</t>
+          <t>todd.barrish@religionofsports.com</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Ongoing via Sunjay</t>
+          <t>ROS team</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Josh (confirm surname)</t>
+          <t>Joey Kravetz</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Straylight Productions</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>Production</t>
-        </is>
-      </c>
+          <t>Religion of Sports</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr"/>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>jtb@straylightprod.co</t>
+          <t>joey.kravetz@religionofsports.com</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Production decks + Becca edits</t>
+          <t>ROS team (Apr)</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Eric Newman</t>
+          <t>Pietro Moro</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>(own production company)</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>Producer — angling for work; intro via Steve Donahue</t>
-        </is>
-      </c>
+          <t>Religion of Sports</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr"/>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>coachenew@gmail.com</t>
+          <t>pietro@religionofsports.com</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Sent names list; SJU coach intro</t>
+          <t>ROS team</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>Active — confirm fit/role</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Geoff Chow</t>
+          <t>Victoria Del Rossi</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>The Ringer / Spotify</t>
+          <t>Candle Studios (Candle Media)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Media / press</t>
+          <t>Exec</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>geoff.chow@theringer.com</t>
+          <t>victoria.delrossi@candlestudios.com</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Press angle (also geoffc@spotify.com)</t>
+          <t>May/June thread</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>Warm — press</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Randy (confirm surname)</t>
+          <t>A. Schneider (confirm)</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Training Ground AI</t>
+          <t>Candle Studios</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Tech / training</t>
+          <t>Exec</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>randy@trainingground.ai</t>
+          <t>aschneider@candlestudios.com</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>June/July thread</t>
+          <t>Ongoing via Sunjay</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Confirm relevance</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Schools (ADs / Coaches / Staff)</t>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Josh (confirm surname)</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Straylight Productions</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>jtb@straylightprod.co</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Production decks + Becca edits</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Steve Donahue</t>
+          <t>Eric Newman</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's (SJU)</t>
+          <t>(own production company)</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Head Men's Basketball Coach</t>
+          <t>Producer — angling for work; intro via Steve Donahue</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>sdonahue1@sju.edu</t>
+          <t>coachenew@gmail.com</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>LOI signed; intro'd Eric Newman</t>
+          <t>Sent names list; SJU coach intro</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>LOI SIGNED — active</t>
+          <t>Active — confirm fit/role</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Tracey Pachman</t>
+          <t>Geoff Chow</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's (SJU)</t>
+          <t>The Ringer / Spotify</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>General Counsel</t>
+          <t>Media / press</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>tpachman@sju.edu</t>
+          <t>geoff.chow@theringer.com</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>On SJU LOI/legal</t>
+          <t>Press angle (also geoffc@spotify.com)</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Warm — press</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Ashwin Puri</t>
+          <t>Randy (confirm surname)</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's (SJU)</t>
+          <t>Training Ground AI</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>CFO — signed the LOI</t>
+          <t>Tech / training</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>apuri@sju.edu</t>
+          <t>randy@trainingground.ai</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>LOI signed 7/29</t>
+          <t>June/July thread</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>LOI SIGNED</t>
+          <t>Confirm relevance</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>Joseph Mihalich</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>Saint Joseph's (SJU)</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>Athletics (confirm title)</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>jmihalich@sju.edu</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>Primary SJU contact since June</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Schools (ADs / Coaches / Staff)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>F. Reynolds (confirm)</t>
+          <t>Steve Donahue</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Marketing VP</t>
+          <t>Head Men's Basketball Coach</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>freynolds@sju.edu</t>
+          <t>sdonahue1@sju.edu</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>SJU marketing</t>
+          <t>LOI signed; intro'd Eric Newman</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -3901,14 +3901,14 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>Contact as needed</t>
+          <t>LOI SIGNED — active</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>K. Welsh (confirm)</t>
+          <t>Tracey Pachman</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Marketing VP</t>
+          <t>General Counsel</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>kwelsh@sju.edu</t>
+          <t>tpachman@sju.edu</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>SJU marketing</t>
+          <t>On SJU LOI/legal</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -3938,14 +3938,14 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>Contact as needed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>E. Laudano (confirm)</t>
+          <t>Ashwin Puri ('Ash')</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3955,128 +3955,128 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Marketing VP</t>
+          <t>Finance/admin — LOI point person</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>elaudano@sju.edu</t>
+          <t>apuri@sju.edu</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>SJU marketing</t>
+          <t>Drove LOI to signature 7/29</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Contact as needed</t>
+          <t>LOI SIGNED — active</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Chris Caputo</t>
+          <t>Lauren Goldsmith</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>George Washington (GW)</t>
+          <t>Saint Joseph's (SJU)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Head Men's Basketball Coach</t>
+          <t>CFO / Treasurer — signed the LOI</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>coachcaputo@gwu.edu</t>
+          <t>(confirm email)</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Championed to his AD</t>
+          <t>Named LOI signatory</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Active — met 8/7</t>
+          <t>LOI SIGNED</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Michael Lipitz</t>
+          <t>Joseph Mihalich</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>George Washington (GW)</t>
+          <t>Saint Joseph's (SJU)</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Athletic Director</t>
+          <t>Athletics (confirm title)</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>michael.lipitz@email.gwu.edu</t>
+          <t>jmihalich@sju.edu</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Met 8/7</t>
+          <t>Primary SJU contact since June</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>Active — follow up</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Chris Clunie</t>
+          <t>F. Reynolds (confirm)</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Saint Joseph's (SJU)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Athletic Director (confirm)</t>
+          <t>Marketing VP</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>chclunie@davidson.edu</t>
+          <t>freynolds@sju.edu</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Davidson (Curry flagship)</t>
+          <t>SJU marketing</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4086,241 +4086,241 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>Active — flagship school</t>
+          <t>Contact as needed</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Nathan Davis</t>
+          <t>K. Welsh (confirm)</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>New Hampshire (UNH)</t>
+          <t>Saint Joseph's (SJU)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Head Coach (confirm)</t>
+          <t>Marketing VP</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>nathan.davis@unh.edu</t>
+          <t>kwelsh@sju.edu</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>LOI draft sent</t>
+          <t>SJU marketing</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Active — LOI in play</t>
+          <t>Contact as needed</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>J. Gallo (confirm)</t>
+          <t>E. Laudano (confirm)</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Merrimack</t>
+          <t>Saint Joseph's (SJU)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>Marketing VP</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>galloj@merrimack.edu</t>
+          <t>elaudano@sju.edu</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Call Aug 19</t>
+          <t>SJU marketing</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>Active — call scheduled</t>
+          <t>Contact as needed</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Seth Needle</t>
+          <t>Chris Caputo</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Temple</t>
+          <t>George Washington (GW)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>(confirm title — mktg/AD)</t>
+          <t>Head Men's Basketball Coach</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>seth.needle@temple.edu</t>
+          <t>coachcaputo@gwu.edu</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>May/June outreach</t>
+          <t>Championed to his AD</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Warm — revisit</t>
+          <t>Active — met 8/7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Daniel Lobacz</t>
+          <t>Michael Lipitz</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Temple</t>
+          <t>George Washington (GW)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>Athletic Director</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>daniel.lobacz@temple.edu</t>
+          <t>michael.lipitz@email.gwu.edu</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>June outreach</t>
+          <t>Met 8/7</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>Warm — revisit</t>
+          <t>Active — follow up</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Matthew Kingsley</t>
+          <t>Chris Clunie</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>Athletic Director</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>matthew.kingsley@yale.edu</t>
+          <t>chclunie@davidson.edu</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>June outreach</t>
+          <t>Davidson (Curry flagship); signed LOI</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Active — flagship school</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Tobe Carberry</t>
+          <t>Austin Buntz</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>GM, Men's &amp; Women's Basketball — handled the Steph Curry LOI</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>tobe.carberry@yale.edu</t>
+          <t>aubuntz@davidson.edu</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>June outreach</t>
+          <t>Signed Davidson LOI (Apr); primary Davidson working contact</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Active — KEY Davidson contact</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Michael Martin</t>
+          <t>D. Phelps (confirm)</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4330,17 +4330,17 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>michael_martin@brown.edu</t>
+          <t>dphelps@fordham.edu</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>May (w/ T. Wheeler)</t>
+          <t>Aug outreach</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -4352,106 +4352,106 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Tyson Wheeler</t>
+          <t>Nathan Davis</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>New Hampshire (UNH)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Coach (confirm)</t>
+          <t>Head Coach (confirm)</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>tyson_wheeler@brown.edu</t>
+          <t>nathan.davis@unh.edu</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>May outreach</t>
+          <t>LOI draft sent</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Active — LOI in play</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>W. Gibson (confirm)</t>
+          <t>J. Gallo (confirm)</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Coach (confirm)</t>
+          <t>(confirm title)</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>gibsonw@hawaii.edu</t>
+          <t>galloj@merrimack.edu</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>July outreach</t>
+          <t>Call Aug 19</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>Warm — revisit</t>
+          <t>Active — call scheduled</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>T. Hammel (confirm)</t>
+          <t>Seth Needle</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>Temple</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>(confirm title)</t>
+          <t>(confirm title — mktg/AD)</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>thammel1@fordham.edu</t>
+          <t>seth.needle@temple.edu</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>May + Aug outreach</t>
+          <t>May/June outreach</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -4463,12 +4463,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>M. Sotsky (confirm)</t>
+          <t>Daniel Lobacz</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Harvard</t>
+          <t>Temple</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -4478,323 +4478,323 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>msotsky@fas.harvard.edu</t>
+          <t>daniel.lobacz@temple.edu</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>July thread</t>
+          <t>June outreach</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>Cold — revisit</t>
+          <t>Warm — revisit</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Chris Herren</t>
+          <t>Matthew Kingsley</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>(former NBA / speaker)</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Talent / advocate</t>
+          <t>(confirm title)</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>chris@chrisherren.com</t>
+          <t>matthew.kingsley@yale.edu</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>'WtW meets hoops' pitch</t>
+          <t>June outreach</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>Warm — follow up</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Legal</t>
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>Tobe Carberry</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Yale</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>(confirm title)</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>tobe.carberry@yale.edu</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>June outreach</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Brian Socolow</t>
+          <t>Michael Martin</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Loeb &amp; Loeb</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Lead counsel (NIL / structure)</t>
+          <t>(confirm title)</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>bsocolow@loeb.com</t>
+          <t>michael_martin@brown.edu</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Engaged; primary legal</t>
+          <t>May (w/ T. Wheeler)</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>Engaged — primary</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>John Kulback</t>
+          <t>Tyson Wheeler</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Loeb &amp; Loeb</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Attorney (w/ Socolow)</t>
+          <t>Coach (confirm)</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>jkulback@loeb.com</t>
+          <t>tyson_wheeler@brown.edu</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>On Loeb threads</t>
+          <t>May outreach</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>Engaged</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>L. Wiznitzer (confirm)</t>
+          <t>W. Gibson (confirm)</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Loeb &amp; Loeb</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>Coach (confirm)</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>lwiznitzer@loeb.com</t>
+          <t>gibsonw@hawaii.edu</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>On Loeb threads</t>
+          <t>July outreach</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>Engaged</t>
+          <t>Warm — revisit</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Robert Freeman</t>
+          <t>T. Hammel (confirm)</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Attorney (lead contact)</t>
+          <t>(confirm title)</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>rfreeman@proskauer.com</t>
+          <t>thammel1@fordham.edu</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Active May</t>
+          <t>May + Aug outreach</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>Confirm current status</t>
+          <t>Warm — revisit</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Grant Darwin</t>
+          <t>M. Sotsky (confirm)</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
+          <t>Harvard</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>(confirm title)</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>gdarwin@proskauer.com</t>
+          <t>msotsky@fas.harvard.edu</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Proskauer team</t>
+          <t>July thread</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Cold — revisit</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Kyle Casazza</t>
+          <t>Chris Herren</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Proskauer Rose</t>
+          <t>(former NBA / speaker)</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>Talent / advocate</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>kcasazza@proskauer.com</t>
+          <t>chris@chrisherren.com</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Proskauer team</t>
+          <t>'WtW meets hoops' pitch</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Warm — follow up</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>Sean Wildes</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>Proskauer Rose</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>swildes@proskauer.com</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>Proskauer team</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
@@ -4803,633 +4803,633 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>Alex Miska</t>
+          <t>Brian Socolow</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Foley &amp; Lardner</t>
+          <t>Loeb &amp; Loeb</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>Lead counsel (NIL / structure)</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>amiska@foley.com</t>
+          <t>bsocolow@loeb.com</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Foley team</t>
+          <t>Engaged; primary legal</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Legal — confirm engagement</t>
+          <t>Engaged — primary</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Trey McDonald</t>
+          <t>John Kulback</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Foley &amp; Lardner</t>
+          <t>Loeb &amp; Loeb</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
+          <t>Attorney (w/ Socolow)</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>jkulback@loeb.com</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>On Loeb threads</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Engaged</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>L. Wiznitzer (confirm)</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Loeb &amp; Loeb</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
           <t>Attorney</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>trey.mcdonald@foley.com</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>Foley team</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Advisory / Academic / Other</t>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>lwiznitzer@loeb.com</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>On Loeb threads</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>R. Bogosian (confirm)</t>
+          <t>Robert Freeman</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Babson College</t>
+          <t>Proskauer Rose</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Faculty / advisor (entrepreneurship)</t>
+          <t>Attorney (lead contact)</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>rbogosian@babson.edu</t>
+          <t>rfreeman@proskauer.com</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>w/ A. Gondal</t>
+          <t>Active May</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Confirm current status</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>A. Gondal (confirm)</t>
+          <t>Grant Darwin</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Babson College</t>
+          <t>Proskauer Rose</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Advisor / student</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>agondal1@babson.edu</t>
+          <t>gdarwin@proskauer.com</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Ongoing June/July</t>
+          <t>Proskauer team</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>G. Randlett (confirm)</t>
+          <t>Kyle Casazza</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Babson College</t>
+          <t>Proskauer Rose</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>grandlett@babson.edu</t>
+          <t>kcasazza@proskauer.com</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>May thread</t>
+          <t>Proskauer team</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>Brett (confirm surname)</t>
+          <t>Sean Wildes</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Bullet Pitch</t>
+          <t>Proskauer Rose</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Pitch/deck vendor (confirm)</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>brett@bulletpitch.com</t>
+          <t>swildes@proskauer.com</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>May thread</t>
+          <t>Proskauer team</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>Vendor — confirm</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>(confirm) oot</t>
+          <t>Alex Miska</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Concert Stuff</t>
+          <t>Foley &amp; Lardner</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Music / events (confirm)</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>oot@concertstuff.com</t>
+          <t>amiska@foley.com</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Ongoing w/ Sunjay to Aug 12</t>
+          <t>Foley team</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>Active — confirm identity</t>
+          <t>Legal — confirm engagement</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>Sofi Selig (confirm)</t>
+          <t>Trey McDonald</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>(confirm org)</t>
+          <t>Foley &amp; Lardner</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Connect</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>sofi.selig@gmail.com</t>
+          <t>trey.mcdonald@foley.com</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>One-off April</t>
+          <t>Foley team</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>P.J. de Silva (confirm)</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>(family?)</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>Personal contact</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>pjdesilva1@gmail.com</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>Apr/May thread</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>Confirm — likely personal/family</t>
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Advisory / Academic / Other</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Cold Outreach — Prospecting (Jan–Mar 2026 blast; firm-level, little/no response unless noted)</t>
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>R. Bogosian (confirm)</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Babson College</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Faculty / advisor (entrepreneurship)</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>rbogosian@babson.edu</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>w/ A. Gondal</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>Advisory</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>RedBird Capital</t>
+          <t>A. Gondal (confirm)</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Sports PE</t>
+          <t>Babson College</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>B. Snow, K. Laforce</t>
+          <t>Advisor / student</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>BSnow@redbirdcap.com</t>
+          <t>agondal1@babson.edu</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Jan 19 cold blast (note: RedBird now in active talks per vault)</t>
+          <t>Ongoing June/July</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>Cold touch → see vault</t>
+          <t>Advisory</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>G. Randlett (confirm)</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>Babson College</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>J. Coulter, T. Sisitsky, J. Evans</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>jcoulter@tpg.com</t>
+          <t>grandlett@babson.edu</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Jan 19 blast</t>
+          <t>May thread</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>No response — revisit</t>
+          <t>Advisory</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Avenue Capital</t>
+          <t>Brett (confirm surname)</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>Bullet Pitch</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Marc Lasry, J. Greenbaum, T. Marcy, S. Chimento</t>
+          <t>Pitch/deck vendor (confirm)</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>mlasry@avenuecapital.com</t>
+          <t>brett@bulletpitch.com</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Jan 19 blast</t>
+          <t>May thread</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED — revisit</t>
+          <t>Vendor — confirm</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>Weatherford Capital</t>
+          <t>(confirm) oot</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Sports PE</t>
+          <t>Concert Stuff</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Will Weatherford</t>
+          <t>Music / events (confirm)</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Will@weatherfordcapital.com</t>
+          <t>oot@concertstuff.com</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Jan 19 blast (also does college-sports PE)</t>
+          <t>Ongoing w/ Sunjay to Aug 12</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>No response — revisit</t>
+          <t>Active — confirm identity</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Seventy Six Capital</t>
+          <t>Sofi Selig (confirm)</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Sports VC</t>
+          <t>(confirm org)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>W. Kimmel, Scott</t>
+          <t>Connect</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>scott@seventysixcapital.com</t>
+          <t>sofi.selig@gmail.com</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Jan 19 blast</t>
+          <t>One-off April</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED — revisit</t>
+          <t>Confirm identity</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>Elysian Park Ventures</t>
+          <t>P.J. de Silva (confirm)</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Sports VC (Dodgers)</t>
+          <t>(family?)</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Pete, Cole</t>
+          <t>Personal contact</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>pete@elysianpark.ventures</t>
+          <t>pjdesilva1@gmail.com</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Jan 19 blast</t>
+          <t>Apr/May thread</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>No response — revisit</t>
+          <t>Confirm — likely personal/family</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Advantage / AV.VC</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>Sports VC</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>Sam, Jeremy; Keaton, Greg</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>sam@advantage.vc</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>Jan 19 blast</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>RESPONDED — revisit</t>
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Cold Outreach — Prospecting (Jan–Mar 2026 blast; firm-level, little/no response unless noted)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>Ryan Sports Ventures</t>
+          <t>RedBird Capital</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Sports VC</t>
+          <t>Sports PE</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>B. Snow, K. Laforce</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>rob@ryansportsventures.com</t>
+          <t>BSnow@redbirdcap.com</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Jan 19 blast</t>
+          <t>Jan 19 cold blast (note: RedBird now in active talks per vault)</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -5439,29 +5439,29 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>Cold touch → see vault</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>TGR / TMRW Sports</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Sports (Tiger Woods)</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Rob, Glenn; info</t>
+          <t>J. Coulter, T. Sisitsky, J. Evans</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>glenn@tgr.ventures</t>
+          <t>jcoulter@tpg.com</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
@@ -5483,22 +5483,22 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>359 Capital</t>
+          <t>Avenue Capital</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Doug, Michael</t>
+          <t>Marc Lasry, J. Greenbaum, T. Marcy, S. Chimento</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>doug@359capital.com</t>
+          <t>mlasry@avenuecapital.com</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -5513,34 +5513,34 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>RESPONDED — revisit</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>Chiron Sports Group</t>
+          <t>Weatherford Capital</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Sports PE</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Will Weatherford</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>sam@chironsportsgroup.com</t>
+          <t>Will@weatherfordcapital.com</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Jan 19 (bounced)</t>
+          <t>Jan 19 blast (also does college-sports PE)</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>Bounced</t>
+          <t>No response — revisit</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>Apex Capital Partners</t>
+          <t>Seventy Six Capital</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>Sports VC</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Koen Bosma</t>
+          <t>W. Kimmel, Scott</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>koen.bosma@apex-cp.com</t>
+          <t>scott@seventysixcapital.com</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -5582,44 +5582,44 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>RESPONDED — revisit</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>Ludis Capital</t>
+          <t>Elysian Park Ventures</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Sports VC</t>
+          <t>Sports VC (Dodgers)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Sam, Matilda, Chris</t>
+          <t>Pete, Cole</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>chris@ludis.capital</t>
+          <t>pete@elysianpark.ventures</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Mar 9 blast</t>
+          <t>Jan 19 blast</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -5631,118 +5631,118 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>Clearlake Capital</t>
+          <t>Advantage / AV.VC</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Sports PE</t>
+          <t>Sports VC</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Todd Boehly, Tony Rosa, D. Groen</t>
+          <t>Sam, Jeremy; Keaton, Greg</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>tboehly@clearlake.com</t>
+          <t>sam@advantage.vc</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Mar 9 blast</t>
+          <t>Jan 19 blast</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>No response — revisit (Boehly)</t>
+          <t>RESPONDED — revisit</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>Haslam Sports Group</t>
+          <t>Ryan Sports Ventures</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Sports (Browns)</t>
+          <t>Sports VC</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Dee Haslam, D. Jenkins</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>deehaslam@haslamsports.com</t>
+          <t>rob@ryansportsventures.com</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Mar 9 blast</t>
+          <t>Jan 19 blast</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>No response — revisit</t>
+          <t>No response</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>Thrive Capital</t>
+          <t>TGR / TMRW Sports</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>VC (Josh Kushner)</t>
+          <t>Sports (Tiger Woods)</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Kareem, Joshua</t>
+          <t>Rob, Glenn; info</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>joshua@thrivecap.com</t>
+          <t>glenn@tgr.ventures</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Mar 9 blast</t>
+          <t>Jan 19 blast</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>No response — revisit</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>Benchmark</t>
+          <t>359 Capital</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5752,22 +5752,22 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Peter, Bill</t>
+          <t>Doug, Michael</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>peter@benchmark.com</t>
+          <t>doug@359capital.com</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Mar 9 blast</t>
+          <t>Jan 19 blast</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -5779,44 +5779,44 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>NFX</t>
+          <t>Chiron Sports Group</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Pete, Gigi, James</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>gigi@nfx.com</t>
+          <t>sam@chironsportsgroup.com</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Mar 9 blast</t>
+          <t>Jan 19 (bounced)</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED — revisit</t>
+          <t>Bounced</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>General Atlantic</t>
+          <t>Apex Capital Partners</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5826,22 +5826,22 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>A. Crisses</t>
+          <t>Koen Bosma</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>acrisses@generalatlantic.com</t>
+          <t>koen.bosma@apex-cp.com</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Mar 9 blast</t>
+          <t>Jan 19 blast</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -5853,22 +5853,22 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>Konvoy VC</t>
+          <t>Ludis Capital</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Sports/gaming VC</t>
+          <t>Sports VC</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Jackson, Jason, Josh</t>
+          <t>Sam, Matilda, Chris</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>jason@konvoy.vc</t>
+          <t>chris@ludis.capital</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -5883,29 +5883,29 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>No response — revisit</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>Founder Collective</t>
+          <t>Clearlake Capital</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>Sports PE</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>David, Eric, Micah</t>
+          <t>Todd Boehly, Tony Rosa, D. Groen</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>eric@foundercollective.com</t>
+          <t>tboehly@clearlake.com</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
@@ -5920,29 +5920,29 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>No response — revisit (Boehly)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>Stripes</t>
+          <t>Haslam Sports Group</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>Sports (Browns)</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Chris, Aidan, Ken</t>
+          <t>Dee Haslam, D. Jenkins</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>ken@stripes.co</t>
+          <t>deehaslam@haslamsports.com</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -5957,29 +5957,29 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>No response — revisit</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>Sharp Alpha Advisors</t>
+          <t>Thrive Capital</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Sports VC</t>
+          <t>VC (Josh Kushner)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Lloyd Danzig</t>
+          <t>Kareem, Joshua</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>lloyd@sharpalphaadvisors.com</t>
+          <t>joshua@thrivecap.com</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -5994,29 +5994,29 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>No response — revisit</t>
+          <t>No response</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>GMF Capital</t>
+          <t>Benchmark</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Denney, Doug</t>
+          <t>Peter, Bill</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>doug@gmfcapital.com</t>
+          <t>peter@benchmark.com</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -6038,22 +6038,22 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>IPR.VC</t>
+          <t>NFX</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Media fund</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Andrea, Timo</t>
+          <t>Pete, Gigi, James</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>timo@ipr.vc</t>
+          <t>gigi@nfx.com</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -6063,34 +6063,34 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>RESPONDED — revisit</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>Boardroom</t>
+          <t>General Atlantic</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Media (Rich Kleiman/Durant)</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Rich</t>
+          <t>A. Crisses</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>rich@boardroom.tv</t>
+          <t>acrisses@generalatlantic.com</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -6105,29 +6105,29 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>No response — revisit</t>
+          <t>No response</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>Alpaca VC</t>
+          <t>Konvoy VC</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>Sports/gaming VC</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Jackson, Jason, Josh</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>david@alpaca.vc</t>
+          <t>jason@konvoy.vc</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -6149,22 +6149,22 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>Candle Media</t>
+          <t>Founder Collective</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Studio (Mayer &amp; Staggs)</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Kevin Mayer, Tom Staggs</t>
+          <t>David, Eric, Micah</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>kevin@candlemedia.com</t>
+          <t>eric@foundercollective.com</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -6179,29 +6179,29 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>No response — revisit</t>
+          <t>No response</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>Fifth Season</t>
+          <t>Stripes</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>L. Zimmermann, M. Lisio, K. Calabrese</t>
+          <t>Chris, Aidan, Ken</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>mlisio@fifthseason.com</t>
+          <t>ken@stripes.co</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -6223,22 +6223,22 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>Pulse Films</t>
+          <t>Sharp Alpha Advisors</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Sports VC</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Mino Jarjoura</t>
+          <t>Lloyd Danzig</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>mino.jarjoura@pulsefilms.com</t>
+          <t>lloyd@sharpalphaadvisors.com</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -6253,76 +6253,76 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>No response — revisit</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>GMF Capital</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Bryan Lourd, Rick Kurtzman, Ethan Kurtzman, C. Carino, J. Darmody, J. MacGregor, T. Brennan</t>
+          <t>Denney, Doug</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>blourd@caa.com</t>
+          <t>doug@gmfcapital.com</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Feb 15+ agency blast</t>
+          <t>Mar 9 blast</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>Mostly no response — a few opens</t>
+          <t>No response</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>WME Entertainment</t>
+          <t>IPR.VC</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Media fund</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>B. Slater, T. Curtis, D. Greenberg, H. Reisch, J. Lesh, N. Towne, S. Mark, W. Lowery, +</t>
+          <t>Andrea, Timo</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>bslater@wmeentertainment.com</t>
+          <t>timo@ipr.vc</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Feb 14-16 blast</t>
+          <t>Mar 9 blast</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -6334,143 +6334,143 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>WME (agency)</t>
+          <t>Boardroom</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Media (Rich Kleiman/Durant)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>M. Jasper (+assistant), M. Berkowitz, S. Rabinowitz</t>
+          <t>Rich</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>mberkowitz@wmeagency.com</t>
+          <t>rich@boardroom.tv</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Feb-Mar blast</t>
+          <t>Mar 9 blast</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>M. Jasper RESPONDED</t>
+          <t>No response — revisit</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>United Talent (UTA)</t>
+          <t>Alpaca VC</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>K. Volchok, J. Barber, N. Gates, B. Lazarus, D. Duchon, K. Lubeck, J. Lawson, S. Sacks, +</t>
+          <t>David</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>volchokk@unitedtalent.com</t>
+          <t>david@alpaca.vc</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Feb 14-16 blast</t>
+          <t>Mar 9 blast</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>K. Volchok RESPONDED</t>
+          <t>No response</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>Range Media Partners</t>
+          <t>Candle Media</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Mgmt/agency</t>
+          <t>Studio (Mayer &amp; Staggs)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Kevin Hussey (Casey Affleck's mgr), Dave Bugliari, P. Orr, A. Glasgow, R. Astphan</t>
+          <t>Kevin Mayer, Tom Staggs</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>khussey@rangemp.com</t>
+          <t>kevin@candlemedia.com</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Feb 14 blast</t>
+          <t>Mar 9 blast</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED (Hussey/Glasgow) — revisit</t>
+          <t>No response — revisit</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>Octagon</t>
+          <t>Fifth Season</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Sports agency</t>
+          <t>Studio</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Jeff Austin</t>
+          <t>L. Zimmermann, M. Lisio, K. Calabrese</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>jeff.austin@octagon.com</t>
+          <t>mlisio@fifthseason.com</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Feb 16 blast</t>
+          <t>Mar 9 blast</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -6482,106 +6482,106 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>Untitled Entertainment</t>
+          <t>Pulse Films</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Mgmt</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>P. Murray</t>
+          <t>Mino Jarjoura</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>pmurray@untitledent.com</t>
+          <t>mino.jarjoura@pulsefilms.com</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Feb 15 blast</t>
+          <t>Mar 9 blast</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED</t>
+          <t>No response</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>Independent Artists Media</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Mgmt</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Dave, Alex</t>
+          <t>Bryan Lourd, Rick Kurtzman, Ethan Kurtzman, C. Carino, J. Darmody, J. MacGregor, T. Brennan</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>dave@independentartistsmedia.com</t>
+          <t>blourd@caa.com</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Feb 14 blast</t>
+          <t>Feb 15+ agency blast</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED</t>
+          <t>Mostly no response — a few opens</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>Red Light Management</t>
+          <t>WME Entertainment</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Music mgmt</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Coran Capshaw</t>
+          <t>B. Slater, T. Curtis, D. Greenberg, H. Reisch, J. Lesh, N. Towne, S. Mark, W. Lowery, +</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>coran.capshaw@redlightmanagement.com</t>
+          <t>bslater@wmeentertainment.com</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Feb 15 blast</t>
+          <t>Feb 14-16 blast</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -6593,183 +6593,442 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>EB Media PR</t>
+          <t>WME (agency)</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Joseph, Ebie</t>
+          <t>M. Jasper (+assistant), M. Berkowitz, S. Rabinowitz</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>ebie@ebmediapr.com</t>
+          <t>mberkowitz@wmeagency.com</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Feb 16 blast</t>
+          <t>Feb-Mar blast</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED</t>
+          <t>M. Jasper RESPONDED</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>Other mgmt/PR (Feb blast)</t>
+          <t>United Talent (UTA)</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Mgmt/PR</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Kipperman, The AMG, Montag Group, Neal Agency, TCC, KP Ent, Make Wake, Yumkas, CSC Biz Mgmt, Price Mgmt, Rowe PR, Rogers&amp;Cowan (Nierob), Leverage, Media4Mgmt, LB Ent</t>
+          <t>K. Volchok, J. Barber, N. Gates, B. Lazarus, D. Duchon, K. Lubeck, J. Lawson, S. Sacks, +</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>(various)</t>
+          <t>volchokk@unitedtalent.com</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Feb 15 blast — see raw list</t>
+          <t>Feb 14-16 blast</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>Mostly no response</t>
+          <t>K. Volchok RESPONDED</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>Andrew Schulz (camp)</t>
+          <t>Range Media Partners</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Comedian/talent</t>
+          <t>Mgmt/agency</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Andrew, Dov, Tanya</t>
+          <t>Kevin Hussey (Casey Affleck's mgr), Dave Bugliari, P. Orr, A. Glasgow, R. Astphan</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>andrew@theandrewschulz.com</t>
+          <t>khussey@rangemp.com</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Cold outreach</t>
+          <t>Feb 14 blast</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>Cold — comedian target</t>
+          <t>RESPONDED (Hussey/Glasgow) — revisit</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>Schools — additional cold</t>
+          <t>Octagon</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>College AD/coach</t>
+          <t>Sports agency</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Holy Cross (Johnson/Paulsen/Rawlings), Stonehill (Kraus), UMBC (Lawson), Loyola (Blue), Coll. of Charleston (Harriman), Northeastern (Janning), BU (Quinn), UPenn</t>
+          <t>Jeff Austin</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>(various .edu)</t>
+          <t>jeff.austin@octagon.com</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Feb–Aug outreach</t>
+          <t>Feb 16 blast</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>Mixed — BU responded; rest cold</t>
+          <t>No response</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
+          <t>Untitled Entertainment</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Mgmt</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>P. Murray</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>pmurray@untitledent.com</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>Feb 15 blast</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>Independent Artists Media</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>Mgmt</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Dave, Alex</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>dave@independentartistsmedia.com</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>Feb 14 blast</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>Red Light Management</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Music mgmt</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Coran Capshaw</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>coran.capshaw@redlightmanagement.com</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>Feb 15 blast</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>EB Media PR</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Joseph, Ebie</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>ebie@ebmediapr.com</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>Feb 16 blast</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>Other mgmt/PR (Feb blast)</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>Mgmt/PR</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Kipperman, The AMG, Montag Group, Neal Agency, TCC, KP Ent, Make Wake, Yumkas, CSC Biz Mgmt, Price Mgmt, Rowe PR, Rogers&amp;Cowan (Nierob), Leverage, Media4Mgmt, LB Ent</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>(various)</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>Feb 15 blast — see raw list</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>Mostly no response</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Schulz (camp)</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Comedian/talent</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Andrew, Dov, Tanya</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>andrew@theandrewschulz.com</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>Cold outreach</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>Cold — comedian target</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>Schools — additional cold</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>College AD/coach</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Holy Cross (Johnson/Paulsen/Rawlings), Stonehill (Kraus), UMBC (Lawson), Loyola (Blue), Coll. of Charleston (Harriman), Northeastern (Janning), BU (Quinn), UPenn</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>(various .edu)</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Aug outreach</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>Mixed — BU responded; rest cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
           <t>O'Melveny &amp; Myers</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>Law firm</t>
         </is>
       </c>
-      <c r="C178" s="3" t="inlineStr">
+      <c r="C185" s="3" t="inlineStr">
         <is>
           <t>Aronson, Reinstein, Afner</t>
         </is>
       </c>
-      <c r="D178" s="3" t="inlineStr">
+      <c r="D185" s="3" t="inlineStr">
         <is>
           <t>baronson@omm.com</t>
         </is>
       </c>
-      <c r="E178" s="3" t="inlineStr">
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>Cold outreach</t>
         </is>
       </c>
-      <c r="F178" s="3" t="inlineStr">
+      <c r="F185" s="3" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="G178" s="3" t="inlineStr">
+      <c r="G185" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
@@ -6778,14 +7037,14 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <mergeCells count="8">
-    <mergeCell ref="A93:G93"/>
-    <mergeCell ref="A116:G116"/>
-    <mergeCell ref="A126:G126"/>
+    <mergeCell ref="A123:G123"/>
+    <mergeCell ref="A141:G141"/>
+    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="A79:G79"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A134:G134"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A133:G133"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6797,7 +7056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7232,7 +7491,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Ludacris &amp; Tim McGraw (CAA); Brian Scalabrine (direct)</t>
+          <t>Ludacris &amp; Tim McGraw (CAA/Gelbard); Brian Scalabrine (direct)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -7243,6 +7502,28 @@
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Agent pass-through active</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Via CAA (Peter Hess / Carla Laur / Rick Lucas)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Colin Jost, Jamie Foxx, Miles Teller, Walton Goggins, Bradley Cooper</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>CAA-repped</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Offers made Mar 2026 — outstanding; revisit</t>
         </is>
       </c>
     </row>

--- a/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
+++ b/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6519,7 +6519,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>CAA</t>
+          <t>CAA / WME / UTA individual agents</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6529,160 +6529,160 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Bryan Lourd, Rick Kurtzman, Ethan Kurtzman, C. Carino, J. Darmody, J. MacGregor, T. Brennan</t>
+          <t>~75 named agents — see dedicated 'Agency Outreach' category below</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>blourd@caa.com</t>
+          <t>(various)</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Feb 15+ agency blast</t>
+          <t>Feb–Mar 2026 blast</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>Mostly no response — a few opens</t>
+          <t>See Agency Outreach category</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>WME Entertainment</t>
+          <t>Range Media Partners</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Mgmt/agency</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>B. Slater, T. Curtis, D. Greenberg, H. Reisch, J. Lesh, N. Towne, S. Mark, W. Lowery, +</t>
+          <t>Kevin Hussey (Casey Affleck's mgr), Dave Bugliari, P. Orr, A. Glasgow, R. Astphan</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>bslater@wmeentertainment.com</t>
+          <t>khussey@rangemp.com</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Feb 14-16 blast</t>
+          <t>Feb 14 blast</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>RESPONDED (Hussey/Glasgow) — revisit</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>WME (agency)</t>
+          <t>Octagon</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Sports agency</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>M. Jasper (+assistant), M. Berkowitz, S. Rabinowitz</t>
+          <t>Jeff Austin</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>mberkowitz@wmeagency.com</t>
+          <t>jeff.austin@octagon.com</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Feb-Mar blast</t>
+          <t>Feb 16 blast</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>M. Jasper RESPONDED</t>
+          <t>No response</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>United Talent (UTA)</t>
+          <t>Untitled Entertainment</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Mgmt</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>K. Volchok, J. Barber, N. Gates, B. Lazarus, D. Duchon, K. Lubeck, J. Lawson, S. Sacks, +</t>
+          <t>P. Murray</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>volchokk@unitedtalent.com</t>
+          <t>pmurray@untitledent.com</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Feb 14-16 blast</t>
+          <t>Feb 15 blast</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>K. Volchok RESPONDED</t>
+          <t>RESPONDED</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>Range Media Partners</t>
+          <t>Independent Artists Media</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Mgmt/agency</t>
+          <t>Mgmt</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Kevin Hussey (Casey Affleck's mgr), Dave Bugliari, P. Orr, A. Glasgow, R. Astphan</t>
+          <t>Dave, Alex</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>khussey@rangemp.com</t>
+          <t>dave@independentartistsmedia.com</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
@@ -6697,39 +6697,39 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED (Hussey/Glasgow) — revisit</t>
+          <t>RESPONDED</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>Octagon</t>
+          <t>Red Light Management</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Sports agency</t>
+          <t>Music mgmt</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Jeff Austin</t>
+          <t>Coran Capshaw</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>jeff.austin@octagon.com</t>
+          <t>coran.capshaw@redlightmanagement.com</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Feb 16 blast</t>
+          <t>Feb 15 blast</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -6741,32 +6741,32 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>Untitled Entertainment</t>
+          <t>EB Media PR</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Mgmt</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>P. Murray</t>
+          <t>Joseph, Ebie</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>pmurray@untitledent.com</t>
+          <t>ebie@ebmediapr.com</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Feb 15 blast</t>
+          <t>Feb 16 blast</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -6778,271 +6778,2758 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>Independent Artists Media</t>
+          <t>Other mgmt/PR (Feb blast)</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Mgmt</t>
+          <t>Mgmt/PR</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Dave, Alex</t>
+          <t>Kipperman, The AMG, Montag Group, Neal Agency, TCC, KP Ent, Make Wake, Yumkas, CSC Biz Mgmt, Price Mgmt, Rowe PR, Rogers&amp;Cowan (Nierob), Leverage, Media4Mgmt, LB Ent</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>dave@independentartistsmedia.com</t>
+          <t>(various)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Feb 14 blast</t>
+          <t>Feb 15 blast — see raw list</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED</t>
+          <t>Mostly no response</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>Red Light Management</t>
+          <t>Andrew Schulz (camp)</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Music mgmt</t>
+          <t>Comedian/talent</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Coran Capshaw</t>
+          <t>Andrew, Dov, Tanya</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>coran.capshaw@redlightmanagement.com</t>
+          <t>andrew@theandrewschulz.com</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Feb 15 blast</t>
+          <t>Cold outreach</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>Cold — comedian target</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>EB Media PR</t>
+          <t>Schools — additional cold</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>College AD/coach</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Joseph, Ebie</t>
+          <t>Holy Cross (Johnson/Paulsen/Rawlings), Stonehill (Kraus), UMBC (Lawson), Loyola (Blue), Coll. of Charleston (Harriman), Northeastern (Janning), BU (Quinn), UPenn</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>ebie@ebmediapr.com</t>
+          <t>(various .edu)</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Feb 16 blast</t>
+          <t>Feb–Aug outreach</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>RESPONDED</t>
+          <t>Mixed — BU responded; rest cold</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>Other mgmt/PR (Feb blast)</t>
+          <t>O'Melveny &amp; Myers</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Mgmt/PR</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Kipperman, The AMG, Montag Group, Neal Agency, TCC, KP Ent, Make Wake, Yumkas, CSC Biz Mgmt, Price Mgmt, Rowe PR, Rogers&amp;Cowan (Nierob), Leverage, Media4Mgmt, LB Ent</t>
+          <t>Aronson, Reinstein, Afner</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>(various)</t>
+          <t>baronson@omm.com</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Feb 15 blast — see raw list</t>
+          <t>Cold outreach</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>Mostly no response</t>
+          <t>Cold</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>Andrew Schulz (camp)</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>Comedian/talent</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>Andrew, Dov, Tanya</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>andrew@theandrewschulz.com</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>Cold outreach</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="inlineStr">
-        <is>
-          <t>Cold — comedian target</t>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Agency Outreach — CAA / WME / UTA (individual agents, Feb–Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>Schools — additional cold</t>
+          <t>Kevin Gelbard</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>College AD/coach</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Holy Cross (Johnson/Paulsen/Rawlings), Stonehill (Kraus), UMBC (Lawson), Loyola (Blue), Coll. of Charleston (Harriman), Northeastern (Janning), BU (Quinn), UPenn</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>(various .edu)</t>
+          <t>kevin.gelbard@caa.com</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Feb–Aug outreach</t>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>Mixed — BU responded; rest cold</t>
+          <t>RESPONDED — Ludacris/Tim McGraw; active</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>O'Melveny &amp; Myers</t>
+          <t>Peter Hess</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>CAA</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Aronson, Reinstein, Afner</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>baronson@omm.com</t>
+          <t>peter.hess@caa.com</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Cold outreach</t>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>RESPONDED — Colin Jost/Foxx/Teller/Cooper/Bateman/Fallon; revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>Carla Laur</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>claur@caa.com</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — Miles Teller/Walton Goggins; revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>Rick Lucas</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>rlucas@caa.com</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — Jamie Foxx; revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>Adam Nettler</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>adam.nettler@caa.com</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — unscripted TV; revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Matt Blake</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>matt.blake@caa.com</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>Landon Shepanek</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>landon.shepanek@caa.com</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>Bryan Lourd</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>blourd@caa.com</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>Christian Carino</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>ccarino@caa.com</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>Rick Kurtzman</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>rkurtzman@caa.com</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>Ethan Kurtzman</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>ethan.kurtzman@caa.com</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>J. Darmody</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>jdarmody@caa.com</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>John MacGregor</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>john.macgregor@caa.com</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>T. Brennan</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>tbrennan@caa.com</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>Matt Wind</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>matt.wind@caa.com</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>Alex Douma</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>alex.douma@caa.com</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>J. Lieberman</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>jlieberman@caa.com</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>Yale Jesser</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>yale.jesser@caa.com</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>David Sherman</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>dsherman@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — existing connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>M. Jasper</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>mjasper@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>T. Curtis</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>tcurtis@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>M. Rudman</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>mrudman@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>R. Koslowsky</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>rkoslowsky@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>DJS</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>djs@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>JZH</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>jzh@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Mathes</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>andrew.mathes@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>M. Maulitz</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>mmaulitz@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>L. Buckley</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>lbuckley@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>T. Jacobs</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>tjacobs@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>S. Conover</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>WME (agency)</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>sconover@wmeagency.com</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>Ari Emanuel (WME CEO)</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>aemanuel@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>Tim Curtis</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>tcurtis@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — offered BU to Carell/Krasinski</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>M. Berkowitz</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>mberkowitz@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>Henry Reisch</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>hreisch@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>Jeff Lesh</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>jlesh@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>Brad Slater</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>bslater@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>Danny Greenberg</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>dgreenberg@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>Nate Towne</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>ntowne@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>Joey Lee</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>leej@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>N. Josephson</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>njosephson@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Finkelstein</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>afinkelstein@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>Douglas Edley</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>dedley@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Dees</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>kdees@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>S. Mark</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>smark@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>W. Lowery</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>wlowery@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>W. Zavala</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>wzavala@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>N. Hoagland</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>nhoagland@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>D. Lucterhand</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>dlucterhand@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>D. Becky</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>dbecky@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>D. Levine</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>dlevine@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>J. Kovacevic</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>jkovacevic@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>jthomas@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>K. Sarkisian</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>ksarkisian@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>T. Bernardy</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>tbernardy@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>R. Rosen</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>rrosen@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>J. Williams</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>jwilliams@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>J. Dixon</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>WME Ent</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>jdixon@wmeentertainment.com</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>K. Volchok</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>volchokk@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>RESPONDED — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>R. Klubeck</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>klubeckr@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>Brett Duchon</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>duchonb@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>Bill Lazarus</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>lazarusb@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>Nancy Gates</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>gatesn@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>Jeremy Barber</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>barberj@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>Jason Heyman</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>heymanj@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>Jacob Lawson</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>lawsonj@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>Greg Janes</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>janeseg@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>Babbette Perry</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>perryb@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>John Sacks</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>sacksj@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>N. Nuciforo</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>nuciforon@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>B. Balbo</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>balbob@unitedtalent.com</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>Feb–Mar 2026 cold outreach ('NCAA Acquisition + Production')</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>Cold — sent, no reply</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A123:G123"/>
     <mergeCell ref="A141:G141"/>
     <mergeCell ref="A97:G97"/>
     <mergeCell ref="A79:G79"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A183:G183"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A133:G133"/>
   </mergeCells>

--- a/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
+++ b/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
@@ -9543,13 +9543,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9560,15 +9561,20 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Celebrity option(s)</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Co-Lead</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Co-Lead</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -9587,256 +9593,272 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Alum / attached (Unanimous)</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>ATTACHED — flagship</t>
+          <t>Ryan Reynolds</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>ATTACHED — flagship; LOI signed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph's</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Kevin Hart, Bradley Cooper, Jason Kelce, Charles Barkley, Will Smith</t>
+          <t>Adam Sandler</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Philly (regional)</t>
+          <t>Triple H</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>LOI signed; celeb TBD (Hart active)</t>
+          <t>Seth Meyers</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>LOI in play (Sandler via Happy Madison)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Tulane</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Woody Harrelson (+ Simu Liu)</t>
+          <t>Denzel Washington</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Film hook (WMCJ)</t>
+          <t>Mike Breen</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>TOP TARGET — warm via Simu</t>
+          <t>Chaz Palminteri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Verified alumni (Denzel, Breen)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Merrimack / Vermont / Northeastern</t>
+          <t>Northeastern</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ben Affleck</t>
+          <t>Mark Wahlberg</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Boston-regional</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Engaging</t>
-        </is>
-      </c>
+          <t>Bill Burr</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>George Washington</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Adam Sandler, Triple H, Seth Meyers</t>
+          <t>Dave Chappelle</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Pharrell Williams</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>LOI in play (Sandler via Happy Madison)</t>
+          <t>Casey Affleck</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Met 8/7 (Caputo/Lipitz) — active</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>Loyola Chicago</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Denzel Washington, Mike Breen</t>
+          <t>Barack Obama</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Verified alumni + hoops</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>On-thesis</t>
-        </is>
-      </c>
+          <t>Tim Grover</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Indiana State</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Larry Bird, David Goggins</t>
+          <t>Ben Affleck</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Bird alum; Goggins geo</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>PMG roster</t>
+          <t>Charlie Day</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Call Aug 19 — active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Central Arkansas</t>
+          <t>St. Joseph's</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Scottie Pippen (+ Clinton/Thornton)</t>
+          <t>Kevin Hart</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Alum</t>
+          <t>Bradley Cooper</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>PMG roster</t>
+          <t>Jason Kelce</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>LOI SIGNED — celeb TBD (Hart active)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Southern Illinois</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Walt 'Clyde' Frazier (+ McCarthy/Odenkirk)</t>
+          <t>Chris Evans</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>All SIU alumni</t>
+          <t>John Krasinski</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>PMG (Frazier) — strong pairing</t>
+          <t>BJ Novak</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Fallen-giant track</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>UMass</t>
+          <t>UMKC</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Julius Erving (+ Richard Gere)</t>
+          <t>Jason Sudeikis</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Alumni</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>PMG (Erving); Dr. J also Philly</t>
-        </is>
-      </c>
+          <t>Paul Rudd</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>UTEP</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Tim Hardaway (+ Glory Road)</t>
+          <t>Dwayne Johnson</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Alum</t>
+          <t>Bruno Mars</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>PMG roster</t>
-        </is>
-      </c>
+          <t>Jason Momoa</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Furman</t>
+          <t>Belmont</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Kevin Garnett</t>
+          <t>Justin Timberlake</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>HS ~20 min away</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Idea (per email)</t>
-        </is>
-      </c>
+          <t>Brad Paisley</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -9851,166 +9873,1076 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Verified alum</t>
+          <t>John A. Sobrato</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Via CTRL / WME</t>
+          <t>Jaylen Williams</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Nash via CTRL / WME</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>Holy Cross</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Bill Murray (via son Luke, HC), Amy Poehler</t>
+          <t>Bill Simmons</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>BC ties</t>
+          <t>Conan O'Brien</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Fallen-giant track</t>
-        </is>
-      </c>
+          <t>Denis Leary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Wake Forest</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Tim Duncan, Muggsy Bogues</t>
+          <t>Ben Affleck</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Verified Deacons</t>
+          <t>Matt Damon</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Fallen-giant track</t>
+          <t>Jason Alexander</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>(WME/Tim Curtis floated Carell + Krasinski)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>NYU (D3)</t>
+          <t>UC Irvine</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Adam Sandler, Billy Crystal, Spike Lee</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Verified Tisch alumni</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>D3 track</t>
-        </is>
-      </c>
+          <t>Will Ferrell</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Johns Hopkins (D3)</t>
+          <t>UC Santa Barbara</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Mike Bloomberg, Michael Phelps, Carmelo Anthony</t>
+          <t>Andrew Schulz</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Alum/local</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>D3 track</t>
+          <t>Michael Douglas</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Schulz camp contacted</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ivy outreach</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Yale, Brown, Harvard staff contacted</t>
+          <t>Jay-Z</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Billy Joel</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Exploratory</t>
-        </is>
-      </c>
+          <t>Ray Dalio</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Reps in motion</t>
+          <t>Tulane</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Ludacris &amp; Tim McGraw (CAA/Gelbard); Brian Scalabrine (direct)</t>
+          <t>The Mannings</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Theo Von</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Agent pass-through active</t>
+          <t>Anthony Mackie</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>TOP TARGET — also Woody Harrelson (via Simu Liu)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Via CAA (Peter Hess / Carla Laur / Rick Lucas)</t>
+          <t>Temple</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Colin Jost, Jamie Foxx, Miles Teller, Walton Goggins, Bradley Cooper</t>
+          <t>Kevin Hart</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>CAA-repped</t>
+          <t>Adam McKay</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Offers made Mar 2026 — outstanding; revisit</t>
+          <t>Judd Apatow</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>(Hart moved to St. Joe's per vault)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>North Texas</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Jamie Foxx</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Post Malone</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Steve Austin</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Foxx via CAA / Rick Lucas</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Keegan-Michael Key</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Eminem</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Bill Murray</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Danny McBride</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Darius Rucker</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Murray = RiverDogs co-owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Justin Bieber</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Dave Burd</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Elon</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Shane Gillis</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Chris Daughtry</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Daughtry≠Elon (verify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Seth MacFarlane</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Charlie Day</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Jay Leno</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Leno≠URI (verify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>UMass</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>John Cena</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Liev Schreiber</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Cena=Springfield(D3); Schreiber≠UMass (verify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Appalachian State</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Eric Church</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Luke Combs</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>William &amp; Mary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Jon Stewart</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Todd Boehly</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Lehigh</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>CJ McCollum</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Dwayne Johnson</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Northern Illinois</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Vince Vaughn</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian Maniscalco</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ball State</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>David Letterman</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Jim Nantz</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Letterman verified; Nantz≠Ball State (verify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Drake</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Jeremy Piven</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Zach Johnson</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Cal State Fullerton</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Costner</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Will Ferrell</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Steve Martin</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Texas Southern</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Michael Strahan</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Travis Scott</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Kent State</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Steve Harvey</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Michael Keaton</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Georgia Southern</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Walton Goggins</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Luke Bryan</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Druski</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Goggins via CAA / Carla Laur</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Georgia State</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Ludacris</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Gucci Mane</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Luda via CAA / Gelbard</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Marshall</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Billy Crystal</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>O.J. Mayo</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Missouri State</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Brad Pitt</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>John Goodman</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Theo Von</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Anthony Mackie</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Texas State</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Taylor Sheridan</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Shawn Michaels</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Wichita State</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Paul Wight</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Antoine Carr</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Oregon State</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Gary Payton</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Indiana State</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Larry Bird</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>John Mellencamp</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Bird/Goggins via PMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Louisiana Monroe</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Tim McGraw</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>McGraw via CAA / Gelbard</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>UTEP</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Tim Hardaway</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>PMG roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Central Arkansas</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Scottie Pippen</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>PMG roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Saint Louis</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Larry Hughes</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Tennessee State</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Oprah Winfrey</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Stanford</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Tiger Woods</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>John McEnroe</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>USC</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Will Ferrell</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Brian Scalabrine</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Scalabrine direct-contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Darius Rucker</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Wake Forest</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Tim Duncan</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Muggsy Bogues</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Verified Deacons</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Providence</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Seth MacFarlane</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Doris Burke</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Burke verified alum</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Hofstra</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Jerry Seinfeld</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Christopher Walken</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>ETSU</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Kenny Chesney</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>John Mayer</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Furman</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Clint Dempsey</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>(Garnett HS nearby — prior note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>School candidate — no lead yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>High Point</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr"/>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>School candidate — no lead yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Loyola Marymount</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr"/>
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>School candidate — no lead yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>VCU</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr"/>
+      <c r="C64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>School candidate — no lead yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>UNC Greensboro</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr"/>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>School candidate — no lead yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr"/>
+      <c r="C66" s="3" t="inlineStr"/>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>School candidate — no lead yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Pepperdine</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr"/>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>School candidate — no lead yet</t>
         </is>
       </c>
     </row>

--- a/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
+++ b/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Celebrity Targets'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -91,7 +92,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9543,38 +9543,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Co-Lead</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Co-Lead</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Suggested Fit 1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Suggested Fit 2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Suggested Fit 3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -9599,6 +9617,21 @@
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>J. Cole</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Anthony Foxx</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>ATTACHED — flagship; LOI signed</t>
         </is>
       </c>
@@ -9626,6 +9659,21 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>Sarah Silverman</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Bode Miller</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Dan Brown</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>LOI in play (Sandler via Happy Madison)</t>
         </is>
       </c>
@@ -9653,6 +9701,21 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Lana Del Rey</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Alan Alda</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Dylan McDermott</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>Verified alumni (Denzel, Breen)</t>
         </is>
       </c>
@@ -9674,7 +9737,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Donnie Wahlberg</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Steve Carell</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Uzo Aduba</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -9699,6 +9777,21 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>Kerry Washington</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Alec Baldwin</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Dave Grohl</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>Met 8/7 (Caputo/Lipitz) — active</t>
         </is>
       </c>
@@ -9720,7 +9813,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Bob Newhart</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Dwyane Wade</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Chance the Rapper</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -9741,6 +9849,21 @@
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
+          <t>Michael Chiklis</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Dane Cook</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Lenny Clarke</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Call Aug 19 — active</t>
         </is>
       </c>
@@ -9768,6 +9891,21 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
+          <t>Will Smith</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Tina Fey</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Bacon</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
           <t>LOI SIGNED — celeb TBD (Hart active)</t>
         </is>
       </c>
@@ -9795,6 +9933,21 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>Amy Poehler</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Doug Flutie</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Chris O'Donnell</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>Fallen-giant track</t>
         </is>
       </c>
@@ -9816,7 +9969,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Eric Stonestreet</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Rob Riggle</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Janelle Monáe</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -9839,7 +10007,22 @@
           <t>Jason Momoa</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Nicole Scherzinger</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Marcus Mariota</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Bethany Hamilton</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -9858,7 +10041,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Trisha Yearwood</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Reese Witherspoon</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Florida Georgia Line</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -9883,6 +10081,21 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
+          <t>Brandi Chastain</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Steve Kerr</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Aisha Tyler</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
           <t>Nash via CTRL / WME</t>
         </is>
       </c>
@@ -9908,7 +10121,22 @@
           <t>Denis Leary</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Bob Cousy</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Tommy Heinsohn</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Chris Matthews</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -9933,6 +10161,21 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>Howard Stern</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Geena Davis</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Julianne Moore</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>(WME/Tim Curtis floated Carell + Krasinski)</t>
         </is>
       </c>
@@ -9950,7 +10193,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Jon Lovitz</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Gwen Stefani</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Mark McGrath</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -9971,6 +10229,21 @@
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t>Katy Perry</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Jack Johnson</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Rob Lowe</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
           <t>Schulz camp contacted</t>
         </is>
       </c>
@@ -9996,7 +10269,22 @@
           <t>Ray Dalio</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Rosie Perez</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Michael Rapaport</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Mike Tyson</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -10021,6 +10309,21 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
+          <t>Harry Connick Jr.</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Lil Wayne</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Wendell Pierce</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
           <t>TOP TARGET — also Woody Harrelson (via Simu Liu)</t>
         </is>
       </c>
@@ -10048,6 +10351,21 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
+          <t>Bob Saget</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Questlove</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Boyz II Men</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
           <t>(Hart moved to St. Joe's per vault)</t>
         </is>
       </c>
@@ -10075,6 +10393,21 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>Don Henley</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Norah Jones</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Roy Orbison</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>Foxx via CAA / Rick Lucas</t>
         </is>
       </c>
@@ -10096,7 +10429,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Big Sean</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Jack White</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Lily Tomlin</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -10121,6 +10469,21 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t>Stephen Colbert</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Thomas Gibson</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Shepard Fairey</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
           <t>Murray = RiverDogs co-owner</t>
         </is>
       </c>
@@ -10142,7 +10505,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Jason Mraz</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Shirley MacLaine</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Warren Beatty</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -10163,6 +10541,21 @@
       <c r="D26" s="3" t="inlineStr"/>
       <c r="E26" s="3" t="inlineStr">
         <is>
+          <t>Ben Folds</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Evan Rachel Wood</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Emily Procter</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
           <t>Daughtry≠Elon (verify)</t>
         </is>
       </c>
@@ -10190,6 +10583,21 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t>Viola Davis</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>James Woods</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Debra Messing</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
           <t>Leno≠URI (verify)</t>
         </is>
       </c>
@@ -10213,6 +10621,21 @@
       <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t>Julius Erving</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Richard Gere</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Jack Welch</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t>Cena=Springfield(D3); Schreiber≠UMass (verify)</t>
         </is>
       </c>
@@ -10234,7 +10657,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Zach Galifianakis</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Ric Flair</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Kellie Pickler</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -10253,7 +10691,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Glenn Close</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Mike Tomlin</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Bruce Hornsby</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -10272,7 +10725,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Amanda Seyfried</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Christine Taylor</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Daniel Roebuck</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -10291,7 +10759,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Dan Castellaneta</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Joan Allen</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>John C. Reilly</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -10312,6 +10795,21 @@
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr">
         <is>
+          <t>Jim Davis</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Joyce DeWitt</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Axl Rose</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
           <t>Letterman verified; Nantz≠Ball State (verify)</t>
         </is>
       </c>
@@ -10333,7 +10831,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Ashton Kutcher</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Wood</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Tom Arnold</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -10356,7 +10869,22 @@
           <t>Steve Martin</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Adam Carolla</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Snoop Dogg</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Jack Black</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -10375,7 +10903,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Megan Thee Stallion</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Beyoncé</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Lizzo</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -10394,7 +10937,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Arsenio Hall</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Chrissie Hynde</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Joe Walsh</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -10419,6 +10977,21 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
+          <t>Jason Aldean</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Alan Jackson</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Killer Mike</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
           <t>Goggins via CAA / Carla Laur</t>
         </is>
       </c>
@@ -10442,6 +11015,21 @@
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr">
         <is>
+          <t>Usher</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Perry</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Jermaine Dupri</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
           <t>Luda via CAA / Gelbard</t>
         </is>
       </c>
@@ -10463,7 +11051,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Randy Moss</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Jason Williams</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Jennifer Garner</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -10482,7 +11085,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Kathleen Turner</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Sheryl Crow</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Jon Hamm</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -10501,7 +11119,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Master P</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Ellen DeGeneres</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Trombone Shorty</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -10520,7 +11153,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>George Strait</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Willie Nelson</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Matthew McConaughey</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -10539,7 +11187,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Xavier McDaniel</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Barry Sanders</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Cliff Levingston</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -10554,7 +11217,22 @@
       </c>
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>A.C. Green</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Danny Ainge</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Ty Burrell</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -10574,6 +11252,21 @@
       </c>
       <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Oscar Robertson</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Adam Driver</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Babyface</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Bird/Goggins via PMG</t>
         </is>
@@ -10594,6 +11287,21 @@
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr">
         <is>
+          <t>Kix Brooks</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Hunter Hayes</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Faith Hill</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
           <t>McGraw via CAA / Gelbard</t>
         </is>
       </c>
@@ -10613,6 +11321,21 @@
       <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="3" t="inlineStr">
         <is>
+          <t>Khalid</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Nate Archibald</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Jones</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
           <t>PMG roster</t>
         </is>
       </c>
@@ -10632,6 +11355,21 @@
       <c r="D49" s="3" t="inlineStr"/>
       <c r="E49" s="3" t="inlineStr">
         <is>
+          <t>Kris Allen</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Billy Bob Thornton</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Mary Steenburgen</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
           <t>PMG roster</t>
         </is>
       </c>
@@ -10653,7 +11391,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Nelly</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Bradley Beal</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Jenna Fischer</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -10668,7 +11421,22 @@
       </c>
       <c r="C51" s="3" t="inlineStr"/>
       <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Miley Cyrus</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Kane Brown</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>CeCe Winans</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -10687,7 +11455,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>John Elway</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Sigourney Weaver</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Luck</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -10708,6 +11491,21 @@
       <c r="D53" s="3" t="inlineStr"/>
       <c r="E53" s="3" t="inlineStr">
         <is>
+          <t>George Lucas</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Forest Whitaker</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>America Ferrera</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
           <t>Scalabrine direct-contacted</t>
         </is>
       </c>
@@ -10725,7 +11523,22 @@
       </c>
       <c r="C54" s="3" t="inlineStr"/>
       <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Aziz Ansari</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Chris Rock</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Leeza Gibbons</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -10746,6 +11559,21 @@
       <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr">
         <is>
+          <t>Chris Paul</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Arnold Palmer</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Josh Howard</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
           <t>Verified Deacons</t>
         </is>
       </c>
@@ -10769,6 +11597,21 @@
       <c r="D56" s="3" t="inlineStr"/>
       <c r="E56" s="3" t="inlineStr">
         <is>
+          <t>Ernie DiGregorio</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>God Shammgod</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Peter Farrelly</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
           <t>Burke verified alum</t>
         </is>
       </c>
@@ -10790,7 +11633,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Francis Ford Coppola</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>James Caan</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Susan Lucci</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -10805,7 +11663,22 @@
       </c>
       <c r="C58" s="3" t="inlineStr"/>
       <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Dolly Parton</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Morgan Wallen</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Keith Jennings</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -10820,7 +11693,22 @@
       </c>
       <c r="C59" s="3" t="inlineStr"/>
       <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Meg Ryan</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Vince McMahon</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Christopher Lloyd</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -10833,11 +11721,30 @@
           <t>Clint Dempsey</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Garnett</t>
+        </is>
+      </c>
       <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>(Garnett HS nearby — prior note)</t>
+          <t>Peabo Bryson</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Marcus Lattimore</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Keith Lockhart</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>KG = Mauldin/Greenville SC regional</t>
         </is>
       </c>
     </row>
@@ -10852,6 +11759,21 @@
       <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="3" t="inlineStr">
         <is>
+          <t>Bill Walton</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Tony Hawk</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Cameron Diaz</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
           <t>School candidate — no lead yet</t>
         </is>
       </c>
@@ -10867,6 +11789,21 @@
       <c r="D62" s="3" t="inlineStr"/>
       <c r="E62" s="3" t="inlineStr">
         <is>
+          <t>Fantasia Barrino</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Rhiannon Giddens</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Randy Travis</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
           <t>School candidate — no lead yet</t>
         </is>
       </c>
@@ -10882,6 +11819,21 @@
       <c r="D63" s="3" t="inlineStr"/>
       <c r="E63" s="3" t="inlineStr">
         <is>
+          <t>Colin Hanks</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Bo Kimble</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Brooke Burke</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
           <t>School candidate — no lead yet</t>
         </is>
       </c>
@@ -10897,6 +11849,21 @@
       <c r="D64" s="3" t="inlineStr"/>
       <c r="E64" s="3" t="inlineStr">
         <is>
+          <t>D'Angelo</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Missy Elliott</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Timbaland</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
           <t>School candidate — no lead yet</t>
         </is>
       </c>
@@ -10912,6 +11879,21 @@
       <c r="D65" s="3" t="inlineStr"/>
       <c r="E65" s="3" t="inlineStr">
         <is>
+          <t>Warren Haynes</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Petey Pablo</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Clay Aiken</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
           <t>School candidate — no lead yet</t>
         </is>
       </c>
@@ -10927,6 +11909,21 @@
       <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="3" t="inlineStr">
         <is>
+          <t>Chauncey Billups</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Tim Allen</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Trey Parker</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
           <t>School candidate — no lead yet</t>
         </is>
       </c>
@@ -10942,11 +11939,27 @@
       <c r="D67" s="3" t="inlineStr"/>
       <c r="E67" s="3" t="inlineStr">
         <is>
+          <t>Doug Christie</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Dick Van Dyke</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Pierce Brosnan</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
           <t>School candidate — no lead yet</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
+++ b/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
@@ -9815,7 +9815,7 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Bob Newhart</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Tommy Heinsohn</t>
+          <t>Billy Collins</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Bob Saget</t>
+          <t>Hall &amp; Oates</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Roy Orbison</t>
+          <t>Erykah Badu</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -10576,11 +10576,7 @@
           <t>Charlie Day</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Jay Leno</t>
-        </is>
-      </c>
+      <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Viola Davis</t>
@@ -10598,7 +10594,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Leno≠URI (verify)</t>
+          <t>Leno removed — no RI tie (Andover MA / LA)</t>
         </is>
       </c>
     </row>
@@ -10626,12 +10622,12 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
+          <t>Marcus Camby</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
           <t>Richard Gere</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Jack Welch</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -11564,7 +11560,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Arnold Palmer</t>
+          <t>Webb Simpson</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -11640,7 +11636,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>James Caan</t>
+          <t>Eddie Murphy</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -11759,7 +11755,7 @@
       <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Bill Walton</t>
+          <t>Mario Lopez</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">

--- a/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
+++ b/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
@@ -10576,7 +10576,11 @@
           <t>Charlie Day</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Jay Leno</t>
+        </is>
+      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Viola Davis</t>
@@ -10594,7 +10598,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Leno removed — no RI tie (Andover MA / LA)</t>
+          <t>Leno = Newport RI resident (Seafair mansion, Ocean Ave)</t>
         </is>
       </c>
     </row>

--- a/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
+++ b/cinderella/Outputs/2026-08-12-cinderella-contacts.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G253"/>
+  <dimension ref="A1:G329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -531,12 +531,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>sunjay.mathews@gmail.com</t>
+          <t>sunjay.mathews@gmail.com / cell +1 973-464-6905</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>On nearly every thread since inception</t>
+          <t>On nearly every thread (414 texts since inception)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>ankur08@gmail.com</t>
+          <t>ankur08@gmail.com / cell +1 917-445-1215</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>greg@6sc.io</t>
+          <t>greg@6sc.io / cell +1 508-692-0121</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Deepen (confirm surname)</t>
+          <t>Deepen Parikh</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -965,17 +965,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Set the Courtside call</t>
+          <t>Partner — set the Courtside call</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>deepen@courtsidevc.com</t>
+          <t>deepen@courtsidevc.com / cell +1 443-562-2282</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Courtside organizer</t>
+          <t>Courtside; also knows Jesse/Jason at SC</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>jj@cherninent.com</t>
+          <t>jj@cherninent.com / cell +1 323-243-0157</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Ben.Simon@gs.com</t>
+          <t>Ben.Simon@gs.com / cell +1 978-399-3434</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Cold outreach</t>
+          <t>Courtside term-sheet update (text)</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -9520,16 +9520,2712 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>iMessage — Schools, Coaches &amp; GMs (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>Joe Mihalich</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>Saint Joseph's</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>+1 716-807-1899 / jmihalich@sju.edu</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>'This is Joe Mihalich, GM at SJU'; Norman editing Hart deck Temple→SJU for him</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>HOT — SJU GM, active</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>Chris Clunie</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>Athletic Director</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>+1 201-328-7311</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>Aug touch-base ('guys are overseas')</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>Active — Davidson AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>Nathan Davis</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Head Coach</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>+1 570-238-2912</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>Sandler/UNH deck + LOI draft</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>Active — UNH HC (Sandler school)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Young</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>BYU (ex-Sixers/87ers)</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>Head Coach</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>+1 678-754-6191</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>Soundboard; 'Steph &amp; Davidson' update</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>Warm — coach ally</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>Dan Lobacz</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>Temple</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Staff / NIL</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>+1 607-237-5849</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>Sent LOI draft; chasing confirm</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>Active — Temple LOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>Seth Needle</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>(SJU/Temple connect)</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>+1 610-761-0283</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>'connect me w/ Andy / Coach Fisher'; call w/ St Joe's</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>Active — SJU connect</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>Dwyane Jones</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>(ex-NBA / Philly)</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>St. Joe's connect</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>+1 610-636-4360</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>'87ers, Kevin Young staff'; SJU-related</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>Warm — SJU connect</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>Dave Paulsen</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>(college HC)</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>+1 570-428-5520</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>Sent deck; 'trustees here this weekend'</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>Warm — coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>Hernando Planells</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>(college coach)</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>+1 919-972-9207</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>Golf-tourney reconnect</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>Warm — coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>Ted Hotaling</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>(college coach)</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>+1 203-444-7544</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>'congrats on D1 transition' cold update</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>Cold — coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>Doug Stewart</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>(college coach)</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>+1 856-261-3313</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>'coach! pick your brain' early concept</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>Cold — coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>Nolan Smith</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>(Duke/Louisville asst)</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>+1 202-805-6947</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>'assistant from your Delaware 87ers days'</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>Cold — coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>Jim McGonigle</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>(Holy Cross connect)</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>HC connect</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>+1 508-287-7059</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>'HC doesn't want to be an NIL school'</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>Cold — HC angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>iMessage — Celebrity Reps, Talent &amp; Production (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>'Boss' Everline</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>Hartbeat Ventures (Kevin Hart)</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Exec</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>+1 405-423-7699 (saved 'Aaron Paul')</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>'you got Boss Everline from Hartbeat here, let's chat'</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>HOT — Hart/Hartbeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>Justin Huchel</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>(Timberlake path)</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>Talent connector</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>+1 310-617-4824</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>Gauging JT interest as lead; wants JT-specific deck</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>Active — JT path</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>Mike Herren</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>(Timberlake path)</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>+1 508-840-5635</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>'I got u Timberlake guy'</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>Active — JT path</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>Max Rudman</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>(talent agent)</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>+1 847-910-0603</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>'send John-specific deck'</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>Warm — agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>Zach Chu</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>(deck/design collaborator)</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>Creative</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>+1 214-364-9224</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>Builds celeb decks (Glenn Powell); La Salle board</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>Active — collaborator</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>David Sherman</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>WME</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>Agent (non-scripted)</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>+1 323-445-4925</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>Steph-specific deck</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>Warm — WME (also in vault)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>Bill Straus</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>(music / production)</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>+1 310-962-8103</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>Production-deck; 'vinyl, NWA'</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>Active — production</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>Alexandre Rockwell</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>(film director)</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>+1 310-415-2305</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>'learning the production world'; LOI update</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>Active — production</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>Lilly Burns</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>Jax Media</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>TV producer</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>+1 917-587-7523</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>Loomis classmate; producer</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>Warm — producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>Scott Manson</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>SpringHill / UNINTERRUPTED (LeBron)</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>+1 310-270-6094</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>SOFI / NIL marketing</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>Warm — LeBron-adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>TJ McConnell</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>Indiana Pacers (NBA)</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>Talent/connector</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>+1 412-980-2620</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>'meeting Hart's team re Temple/St Joe's'</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>Warm — NBA connect</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>Chris Herren</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>(ex-NBA / speaker)</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>Talent/connector</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>+1 401-626-2445</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>Intro via Mike; NIL project</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>Josh Altman</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>(Million Dollar Listing)</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>Talent/connector</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>+1 323-610-0231</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>'need a celeb' pitch</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>Ken Jeong</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>(actor)</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>Talent</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>+1 310-779-8260</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>Steph/Davidson update</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>Cold — talent</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>Jordan Fliegel</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>(CoachUp founder / VC)</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>+1 617-943-8750</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>'congrats on Miami move, new business'</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>Tim Grover</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>(trainer — MJ/Kobe)</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>Trainer/rep</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>+1 312-823-2320</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>Cold concept pitch</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>Cold — trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>Rod Baker</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>(MSA-adjacent)</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>+1 585-451-3235</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>'MSA floated LeBron/Akron'</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>iMessage — Capital &amp; Investors (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>Josh Bennett</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>(investor, NH)</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>+1 603-387-2068</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>'deck received, keep chatting'</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>Active — investor</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>Alan Chang</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>(sports-biz investor)</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>+1 702-292-5700</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>Deck Qs on celeb comp</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>Noah Yates</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>Y Investments</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>+1 732-608-3499</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>'no bandwidth for parentco right now'</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>Passed — revisit</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>Jay Jackson</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>(principal / advisor)</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>+1 310-503-0419</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>Formal comms; input on names</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>Active — advisor</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Glass</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>(investor/advisor)</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>+1 201-563-1919</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>'this is fantastic — how I envisioned it'</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>Warm — enthusiastic</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>Jameson Davis</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>DraftKings (VIP)</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>Connector/investor</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>+1 617-631-2530</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>Early concept</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>Esteban Arguello</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>(investor)</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>+1 661-993-8226</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>Deck + numbers</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>Michael Siegel</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>(investor)</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>+1 610-517-3836</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>Coaches-NIL venture</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>Gibson Johnson</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>(investor)</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>+1 385-209-4481</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>/dj deck</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>Jonathan Chang</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>(investor, Seattle)</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>+1 425-894-5051</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>Steph/Davidson news; term-sheet interest</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Hussey</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>(investor/connector)</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>+1 310-499-8239</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>RedBird NYC meeting</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Volchok</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>(investor/advisor)</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>+1 310-508-5000</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>Portal timing</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>Brendan Greeley</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>(investor/advisor)</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>+1 312-330-5316</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>Docu-series structure</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>Gregory Bush</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>(investor)</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>+1 631-495-4763</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>'raised $12M' pitch</t>
+        </is>
+      </c>
+      <c r="F300" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>Chad Hutchinson</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>(finance / ex-athlete)</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>+1 214-957-7861</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>Cold VC update</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>Mike Wenzell</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>(China basketball)</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>+86 185-1454-0553</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>'navigating the system over there'</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>Warm — China</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>iMessage — Advisors, Connectors &amp; Soundboards (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>Nate Fritsch</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>(advisor)</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>+1 919-475-2625</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>Davidson / Hun / Matt McKillop connect; deck feedback</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>Active — Davidson advisor (also in DB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>Chris Caputo</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>George Washington</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>Head Coach</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>+1 786-877-2864</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>Woj connected; LOIs Davidson/SJU</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>Active — GW HC</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>Erick Peyton</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>Unanimous Media (Curry)</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>+1 323-899-5748</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>'UM / Davidson status'</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>Active — Curry/Unanimous</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>Adrian Williams</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>SC Holdings</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>+1 404-421-0361</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>Relays Erick / term sheet</t>
+        </is>
+      </c>
+      <c r="F307" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>Becca (Rebecca) Gitlitz</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>Exec</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>+1 201-669-6884</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Luck/Stanford NIL tidbit</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>Active — EverWonder</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>Deirdre Fenton</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>EverWonder</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>Exec</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>+1 646-275-6540</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>Intro thread</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>Active — EverWonder</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>Eric Newman</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>(production via Donahue)</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>Producer</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>+1 516-965-3507</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>Meeting set w/ Sunjay</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>Jeremy Peschka</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>(media/connector)</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>+1 971-285-6078</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>Peacock docuseries intel; Kevin O'Leary path</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>Varun Sudhakar</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>(advisor, UK)</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>Advisor / model</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>+1 609-433-1085</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>Works the financial model; USC-NIL contact via Nigel</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>Active — model</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>Alex Miska</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>Foley &amp; Lardner</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>+1 908-500-1063</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>'Luke Murray congrats'; term-sheet help</t>
+        </is>
+      </c>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>Warm — legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>Shavlik Randolph</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>(ex-NBA)</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>Advisor/connector</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>+1 919-539-1309</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>Wrexham-concept riffing</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>Warm — ex-NBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Owens</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>(NIL operator)</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>Peer operator</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>+1 973-303-1637</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>'raised $ for NIL play'; Hart-team meetings</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>Warm — peer</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>Tom Baudinet</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>(advisor)</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>+1 203-695-4381</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>'chatting with KY... NCAA/NIL insight'</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>Austin Buntz</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>(creative)</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>Creative</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>+1 570-579-6181</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>Wrote Wrexham pitch; building deck w/ Jesse</t>
+        </is>
+      </c>
+      <c r="F317" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G317" s="3" t="inlineStr">
+        <is>
+          <t>Active — creative</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>Dane Diliegro</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>(actor/athlete)</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>+1 781-589-0820</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>Concept soundboard</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>Steve Ceruti</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>Barstool (Russillo)</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>Media connect</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>+1 860-302-2869</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>Barstool/Russillo; Affleck-agent feedback</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G319" s="3" t="inlineStr">
+        <is>
+          <t>Warm — media</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>Mike Sotsky</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>Harvard Basketball</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>+1 201-956-0883</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>'showed TA the deck'</t>
+        </is>
+      </c>
+      <c r="F320" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>Warm — Harvard</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>Matt Janning</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>(ex-pro player)</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>+1 612-867-8797</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>Wahlberg proposal</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G321" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>Conor Stevens</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>(Stevens family)</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>Personal ally</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>+1 617-610-1327</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>Davidson/Steph update</t>
+        </is>
+      </c>
+      <c r="F322" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G322" s="3" t="inlineStr">
+        <is>
+          <t>Ally</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>Ryan Cain</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>(coach/friend)</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>Soundboard</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>+1 508-873-5005</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="inlineStr">
+        <is>
+          <t>School-openness question</t>
+        </is>
+      </c>
+      <c r="F323" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G323" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>Joey Flannery</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>(peer)</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>Soundboard</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>+1 978-303-7677</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>Pitch narrative</t>
+        </is>
+      </c>
+      <c r="F324" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G324" s="3" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>Brendan Lang</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>(advisor)</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>+1 774-263-2705</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="inlineStr">
+        <is>
+          <t>BYU collectives insight</t>
+        </is>
+      </c>
+      <c r="F325" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="G325" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>Mark Palmieri</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>(advisor)</t>
+        </is>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>+1 203-641-4518</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>Ivy/NIL note</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G326" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>Matt Blue</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>(connector)</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>+1 508-254-4752</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="inlineStr">
+        <is>
+          <t>Celeb sourcing</t>
+        </is>
+      </c>
+      <c r="F327" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G327" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>Arthur Lynch</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>(ex-NFL)</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>Soundboard</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>+1 508-369-0782</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>Deck review</t>
+        </is>
+      </c>
+      <c r="F328" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="G328" s="3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>Cliff Furtado</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>(friend)</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>Legal referral</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>+1 508-491-7250</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="inlineStr">
+        <is>
+          <t>Lawyer refs for term sheet</t>
+        </is>
+      </c>
+      <c r="F329" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G329" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
-  <mergeCells count="9">
+  <mergeCells count="13">
     <mergeCell ref="A123:G123"/>
     <mergeCell ref="A141:G141"/>
+    <mergeCell ref="A254:G254"/>
+    <mergeCell ref="A286:G286"/>
     <mergeCell ref="A97:G97"/>
+    <mergeCell ref="A303:G303"/>
     <mergeCell ref="A79:G79"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A183:G183"/>
+    <mergeCell ref="A268:G268"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A133:G133"/>
   </mergeCells>
